--- a/multiset_202604/fmo_300k/plot/multiset_16bd_thermo.xlsx
+++ b/multiset_202604/fmo_300k/plot/multiset_16bd_thermo.xlsx
@@ -413,5757 +413,5803 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G250"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9.999999997737658e-21</v>
+        <v>9.999999997737616e-21</v>
       </c>
       <c r="B1" t="n">
         <v>1.000000000008489e-20</v>
       </c>
       <c r="C1" t="n">
-        <v>9.999999999727532e-21</v>
+        <v>9.999999999727548e-21</v>
       </c>
       <c r="D1" t="n">
         <v>1</v>
       </c>
       <c r="E1" t="n">
-        <v>9.99999999777336e-21</v>
+        <v>9.999999997773135e-21</v>
       </c>
       <c r="F1" t="n">
-        <v>9.999999997817602e-21</v>
+        <v>9.999999997817366e-21</v>
       </c>
       <c r="G1" t="n">
-        <v>9.999999997693188e-21</v>
+        <v>9.999999997692935e-21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.2971183145336e-05</v>
+        <v>5.296850182321304e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>2.601710027037235e-05</v>
+        <v>2.601502214281169e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.953460330455844e-05</v>
+        <v>1.953498732720424e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9947179651208317</v>
+        <v>0.9947190802408619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005087764101043992</v>
+        <v>0.005086668873581644</v>
       </c>
       <c r="F2" t="n">
-        <v>1.926189425157773e-05</v>
+        <v>1.926073756806663e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.648599715226222e-05</v>
+        <v>7.647163669527432e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0002100128184305037</v>
+        <v>0.0002099717135717785</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001038376120849802</v>
+        <v>0.0001038024757342916</v>
       </c>
       <c r="C3" t="n">
-        <v>8.29083648723899e-05</v>
+        <v>8.291170195422231e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9790641503910983</v>
+        <v>0.9790702150507798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02015506947122257</v>
+        <v>0.02014919835126019</v>
       </c>
       <c r="F3" t="n">
-        <v>7.861148851486391e-05</v>
+        <v>7.859162968729708e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003054098537764835</v>
+        <v>0.0003053090770124878</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.000465648472464</v>
+        <v>0.0004655812765895262</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0002328733467028747</v>
+        <v>0.0002327835516975599</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002038429822788404</v>
+        <v>0.000203866717161317</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9536015641150587</v>
+        <v>0.9536117014375808</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04462840756500365</v>
+        <v>0.0446186121109438</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001825734473207739</v>
+        <v>0.0001825335557903654</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006850900711711171</v>
+        <v>0.0006849213502367898</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008109621727925487</v>
+        <v>0.0008108970084458911</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0004122824732452222</v>
+        <v>0.000412123580155673</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004032044270282203</v>
+        <v>0.0004032640406069971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.919229726931216</v>
+        <v>0.919237764804486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0775933279699957</v>
+        <v>0.07758570896805715</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003380463049695714</v>
+        <v>0.0003379870889231687</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001212449720752607</v>
+        <v>0.001212254509324636</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.001233888296119439</v>
+        <v>0.001233837649414635</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006411446696595681</v>
+        <v>0.0006409005867027041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0007062462281878857</v>
+        <v>0.0007063643971781292</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8771295465466467</v>
+        <v>0.8771328665972519</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1178534087070316</v>
+        <v>0.1178505585868904</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005533656370992206</v>
+        <v>0.0005532831505389315</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001882399915255866</v>
+        <v>0.001882189032023176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.00171968426792037</v>
+        <v>0.001719631520238549</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009186497155710757</v>
+        <v>0.0009183113057891505</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001139343525118432</v>
+        <v>0.001139556904581563</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8287034614106804</v>
+        <v>0.8287025957172958</v>
       </c>
       <c r="E7" t="n">
-        <v>0.163994479172306</v>
+        <v>0.1639958850360838</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008371633258333974</v>
+        <v>0.0008370533436751695</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002687218582569968</v>
+        <v>0.002686966172335997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002251493835200571</v>
+        <v>0.002251408179959022</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001244306814451918</v>
+        <v>0.001243886472873008</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001726680872434345</v>
+        <v>0.001727029276655232</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7755061315417084</v>
+        <v>0.775502001667032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2144581682617639</v>
+        <v>0.2144628952283255</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001197147156372042</v>
+        <v>0.001197036600689436</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003616071518068957</v>
+        <v>0.003615742574465882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002811094227393677</v>
+        <v>0.002810934228219041</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001618083990798602</v>
+        <v>0.001617597487381137</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002487269222898288</v>
+        <v>0.002487798444656834</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7191695752929436</v>
+        <v>0.7191629134024652</v>
       </c>
       <c r="E9" t="n">
-        <v>0.267620258735868</v>
+        <v>0.2676275577798529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001638964112824643</v>
+        <v>0.001638887085563077</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004654754417273341</v>
+        <v>0.004654311571861557</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.003379773414844941</v>
+        <v>0.003379491342573118</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002040482952311632</v>
+        <v>0.002039938044930471</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003432726810644003</v>
+        <v>0.00343348580560333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6613330414926103</v>
+        <v>0.6613244923020288</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3218630251396541</v>
+        <v>0.3218722589127359</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002165179303195116</v>
+        <v>0.002165152384534985</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005785770886739985</v>
+        <v>0.005785181207592793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.003939262687736731</v>
+        <v>0.003938817077418587</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002512517524760155</v>
+        <v>0.002511915100192765</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004566054366421703</v>
+        <v>0.0045670745783966</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6035807235753076</v>
+        <v>0.6035709088578527</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3756382422322619</v>
+        <v>0.3756488175546489</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002774483551487217</v>
+        <v>0.002774515652462026</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006988716062024295</v>
+        <v>0.006987951179028531</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004472719548459078</v>
+        <v>0.004472068483499177</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003035579548800007</v>
+        <v>0.003034925800971623</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005881420292750066</v>
+        <v>0.005882706548665018</v>
       </c>
       <c r="D12" t="n">
-        <v>0.54738927152676</v>
+        <v>0.5473786752357706</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4275187989668593</v>
+        <v>0.427530276381522</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003461230630637589</v>
+        <v>0.003461334239182259</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008240979485733822</v>
+        <v>0.008240013310389401</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00496563861677112</v>
+        <v>0.004964741994740927</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003611214733659263</v>
+        <v>0.003610522503277263</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007364988486318612</v>
+        <v>0.007366522593189559</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4940855258415729</v>
+        <v>0.4940743994960065</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4762386095320744</v>
+        <v>0.476250784050901</v>
       </c>
       <c r="F13" t="n">
-        <v>0.004215324656532565</v>
+        <v>0.004215523293324474</v>
       </c>
       <c r="G13" t="n">
-        <v>0.009518698133071221</v>
+        <v>0.009517506068560406</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.00540666287045483</v>
+        <v>0.005405484743035935</v>
       </c>
       <c r="B14" t="n">
-        <v>0.004240801002512059</v>
+        <v>0.00424008710653557</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0089965202269967</v>
+        <v>0.008998303007817671</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4448147432714257</v>
+        <v>0.4448031690506107</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5207209295209113</v>
+        <v>0.520733732869665</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005022498222126055</v>
+        <v>0.005022818629418072</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01079784488557321</v>
+        <v>0.01079640459291702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.005788202653375684</v>
+        <v>0.00578671715010513</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004925154359660379</v>
+        <v>0.004924435045150786</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01075153242501951</v>
+        <v>0.01075362898216903</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4005187833456592</v>
+        <v>0.4005067904661958</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5600960127770133</v>
+        <v>0.5601093720778355</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005864967048178685</v>
+        <v>0.005865410824812228</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01205534739109337</v>
+        <v>0.01205364545373164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.006106843330310879</v>
+        <v>0.006105031558287926</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00566407404557755</v>
+        <v>0.005663365212964503</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0126037144003329</v>
+        <v>0.01260626508990763</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3619232572674965</v>
+        <v>0.3619109602497783</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5937095905342459</v>
+        <v>0.5937232779953442</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006722369200027193</v>
+        <v>0.00672291274096088</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01327015122200887</v>
+        <v>0.01326818715275612</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.006363474660077188</v>
+        <v>0.00636132736132309</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006455893961300732</v>
+        <v>0.006455205273033636</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01452726943265825</v>
+        <v>0.01453045881779245</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3295324902454029</v>
+        <v>0.3295203276841985</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6211237743479834</v>
+        <v>0.621137191189445</v>
       </c>
       <c r="F17" t="n">
-        <v>0.007572987515385663</v>
+        <v>0.007573592580184971</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01442410983719191</v>
+        <v>0.01442189709402225</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.006563159700679591</v>
+        <v>0.006560669032684843</v>
       </c>
       <c r="B18" t="n">
-        <v>0.007297067555165827</v>
+        <v>0.007296398423949617</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01649893765718902</v>
+        <v>0.01650295396268702</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3036314499042624</v>
+        <v>0.3036204316803898</v>
       </c>
       <c r="E18" t="n">
-        <v>0.642111577290188</v>
+        <v>0.6421235649285717</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008395175129252523</v>
+        <v>0.008395791260494377</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01550263276326245</v>
+        <v>0.01550019071122291</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.006714738558890846</v>
+        <v>0.006711887851399553</v>
       </c>
       <c r="B19" t="n">
-        <v>0.008181823624089554</v>
+        <v>0.008181169037141197</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01849951022761219</v>
+        <v>0.01850452531250617</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2842938117404429</v>
+        <v>0.2842856102195235</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6566461926511782</v>
+        <v>0.6566549883344024</v>
       </c>
       <c r="F19" t="n">
-        <v>0.009168852850902517</v>
+        <v>0.009169417063628045</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01649507034688375</v>
+        <v>0.01649240218139889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.00683020744722732</v>
+        <v>0.00682697093270303</v>
       </c>
       <c r="B20" t="n">
-        <v>0.009101952033073847</v>
+        <v>0.009101308329121705</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0205147443003055</v>
+        <v>0.02052090569746224</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2713952617865289</v>
+        <v>0.271391971644143</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6648860545143404</v>
+        <v>0.6648895526188293</v>
       </c>
       <c r="F20" t="n">
-        <v>0.009876958688531428</v>
+        <v>0.009877396426230801</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01739482122999272</v>
+        <v>0.01739189435150968</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.006923928844891826</v>
+        <v>0.006920282408210446</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01004676404374267</v>
+        <v>0.01004612468113199</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02253566092321599</v>
+        <v>0.0225431044524605</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2646314688556088</v>
+        <v>0.2646351250985564</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6671562608587731</v>
+        <v>0.6671524688723885</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01050673155230706</v>
+        <v>0.01050696676763656</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01819918492146085</v>
+        <v>0.01819592771961537</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.007011730320849334</v>
+        <v>0.007007658981476416</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01100324294250662</v>
+        <v>0.01100260518200172</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02455829653903178</v>
+        <v>0.0245671814989701</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2635399466751751</v>
+        <v>0.2635520494658745</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6639270882246776</v>
+        <v>0.6639145348100346</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01105068835689748</v>
+        <v>0.01105065197031195</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01890900694086207</v>
+        <v>0.01890531809133088</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007109961906665197</v>
+        <v>0.007105456866934686</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01195639650991823</v>
+        <v>0.011955769094896</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02658299965216807</v>
+        <v>0.02659356435642233</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2675250885599969</v>
+        <v>0.2675460314848835</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6557901718883694</v>
+        <v>0.6557684034733987</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01150720388680216</v>
+        <v>0.01150683419314531</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01952817759608021</v>
+        <v>0.01952394053031938</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.00723457144146532</v>
+        <v>0.007229616777225437</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01288980540588146</v>
+        <v>0.0128892028650101</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02861340702552648</v>
+        <v>0.02862599389653572</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2758850174153555</v>
+        <v>0.2759138801966818</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6434335040346018</v>
+        <v>0.6434032687409926</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0118806529215169</v>
+        <v>0.0118799056344898</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02006304175565248</v>
+        <v>0.02005813188906514</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.007400243721519342</v>
+        <v>0.007394803879576909</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0137863449133215</v>
+        <v>0.01378577376866452</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03065527638907182</v>
+        <v>0.03067027691357768</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2878392814088859</v>
+        <v>0.2878744604552438</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6276159933479059</v>
+        <v>0.6275786836985329</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01218108450407841</v>
+        <v>0.01217995153067593</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02052177571521709</v>
+        <v>0.02051604975372822</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.007619651112616299</v>
+        <v>0.007613667991165038</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01462902267209794</v>
+        <v>0.01462846579304257</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0327152126658878</v>
+        <v>0.03273302132286988</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3025582264738979</v>
+        <v>0.3025980368757976</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6091406632095698</v>
+        <v>0.6090977691218237</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01242345574779546</v>
+        <v>0.01242199505458279</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02091376811813503</v>
+        <v>0.02090704384071839</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.007902858918873035</v>
+        <v>0.007896258220617625</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01540188529227468</v>
+        <v>0.01540128713998424</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03479940871620342</v>
+        <v>0.03482042356001898</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3191928792710065</v>
+        <v>0.3192356280710812</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5888274261421768</v>
+        <v>0.588780459950842</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01262651728752628</v>
+        <v>0.01262486814803733</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02124902437193936</v>
+        <v>0.02124107490941851</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.008256907543741332</v>
+        <v>0.00824960585677603</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01609092703359637</v>
+        <v>0.01609017931239753</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03691259927351901</v>
+        <v>0.03693724611386659</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3369033193403878</v>
+        <v>0.3369471628577586</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5674871705880661</v>
+        <v>0.5674377887218101</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01281143529674713</v>
+        <v>0.01280980885108824</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02153764092394214</v>
+        <v>0.0215282082863028</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.0086855706745758</v>
+        <v>0.008677485756900038</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01668489888267306</v>
+        <v>0.01668384726359676</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0390572804051117</v>
+        <v>0.03908597369059669</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3548849376157739</v>
+        <v>0.3549277991487843</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5458976548617868</v>
+        <v>0.5458477627337458</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01300027344677533</v>
+        <v>0.01299893273130304</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0217893841133034</v>
+        <v>0.02177819867507333</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.009189299422391932</v>
+        <v>0.009180359027028439</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01717597185014631</v>
+        <v>0.01717443748498955</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0412331945317743</v>
+        <v>0.0412662409040138</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3723921889464686</v>
+        <v>0.3724318122130952</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5247814950919749</v>
+        <v>0.5247332622686715</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01321447784240948</v>
+        <v>0.01321373034411525</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0220133723148349</v>
+        <v>0.02200015775808647</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.009765344791095094</v>
+        <v>0.009755497299515192</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0175602200242008</v>
+        <v>0.0175580189412917</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04343709119387415</v>
+        <v>0.04347461249720331</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3887592503503758</v>
+        <v>0.3887933914373231</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5047867574234032</v>
+        <v>0.504742475413169</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01347349746793499</v>
+        <v>0.01347369172845561</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02221783874911607</v>
+        <v>0.02220231268304221</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.01040803427230869</v>
+        <v>0.01039725571450818</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01783787610349884</v>
+        <v>0.01783482337600035</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04566278559061186</v>
+        <v>0.04570471021417389</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4034170948860142</v>
+        <v>0.4034437273091126</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4864706213501639</v>
+        <v>0.4864324909898146</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01379364232234874</v>
+        <v>0.01379515203778984</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02240994547505392</v>
+        <v>0.02239184035860085</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01110917088045556</v>
+        <v>0.01109746600193387</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01801332013216097</v>
+        <v>0.01800922606430382</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04790149392898166</v>
+        <v>0.04794757345447273</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4159064275758048</v>
+        <v>0.4159237636430363</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4702866624391119</v>
+        <v>0.4702567513744462</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01418725796926572</v>
+        <v>0.01419045321675255</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02259566707421942</v>
+        <v>0.02257476624505431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.01185852280268123</v>
+        <v>0.01184592268355439</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01809480088261773</v>
+        <v>0.01808947295809476</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05014239099092385</v>
+        <v>0.05019222400008081</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4258859983957629</v>
+        <v>0.4258923531211864</v>
       </c>
       <c r="E34" t="n">
-        <v>0.456576277452362</v>
+        <v>0.4565566155850226</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01466226828946414</v>
+        <v>0.01466748945519301</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02277974118618826</v>
+        <v>0.02275592219686832</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.01264436945520034</v>
+        <v>0.01263092550083936</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01809392441150022</v>
+        <v>0.01808717519000197</v>
       </c>
       <c r="C35" t="n">
-        <v>0.05237332357639408</v>
+        <v>0.05242637016768892</v>
       </c>
       <c r="D35" t="n">
-        <v>0.433136017451609</v>
+        <v>0.4331296600906661</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4455645818149552</v>
+        <v>0.4455572915903264</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01522209306535</v>
+        <v>0.01522962674131552</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02296569022499122</v>
+        <v>0.02293895071916148</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.01345407337474955</v>
+        <v>0.01343984786827572</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01802495479239904</v>
+        <v>0.01801660755974548</v>
       </c>
       <c r="C36" t="n">
-        <v>0.05458160493990428</v>
+        <v>0.05463718010415503</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4375568177645049</v>
+        <v>0.4375358352745367</v>
       </c>
       <c r="E36" t="n">
-        <v>0.437360755541544</v>
+        <v>0.4373682258750783</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01586590128377782</v>
+        <v>0.01587595734406079</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02315589230312046</v>
+        <v>0.02312634597414818</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01427465090862455</v>
+        <v>0.01425970699361954</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01790398038237757</v>
+        <v>0.01789387092188437</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05675483314334429</v>
+        <v>0.05681210402146468</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4391630616846368</v>
+        <v>0.4391251871880061</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4319626665093796</v>
+        <v>0.4319877656723559</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01658913939733402</v>
+        <v>0.01660183592298093</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02335166797430357</v>
+        <v>0.02331952927968825</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.01509331538538137</v>
+        <v>0.01507770631607551</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01774801385448302</v>
+        <v>0.01773598675392049</v>
       </c>
       <c r="C38" t="n">
-        <v>0.05888167762251353</v>
+        <v>0.05893967347203353</v>
       </c>
       <c r="D38" t="n">
-        <v>0.438073756268554</v>
+        <v>0.4380162326924018</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4292655950310161</v>
+        <v>0.4293118376809208</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01738425204049423</v>
+        <v>0.01739960928780927</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02355338979755762</v>
+        <v>0.02351895379683878</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.01589796791606564</v>
+        <v>0.01588172288553394</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01757409392139097</v>
+        <v>0.01755999352852948</v>
       </c>
       <c r="C39" t="n">
-        <v>0.06095256182352533</v>
+        <v>0.06101018295508635</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4344987307855937</v>
+        <v>0.4344184074721171</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4290745196249184</v>
+        <v>0.4291460046730494</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01824150426545901</v>
+        <v>0.01825944930825234</v>
       </c>
       <c r="G39" t="n">
-        <v>0.02376062166304708</v>
+        <v>0.02372423917743114</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.01667761357541467</v>
+        <v>0.0166607181561528</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0173984503268353</v>
+        <v>0.01738211195950258</v>
       </c>
       <c r="C40" t="n">
-        <v>0.06296016571418613</v>
+        <v>0.06301620375403999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4287228859784452</v>
+        <v>0.4286163846123895</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4311187896523542</v>
+        <v>0.4312200451867084</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01914981894120023</v>
+        <v>0.01917020450218931</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02397227581156471</v>
+        <v>0.02393433182901741</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.0174226882260698</v>
+        <v>0.01740505793913123</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01723578276960135</v>
+        <v>0.01721703127092683</v>
       </c>
       <c r="C41" t="n">
-        <v>0.06489972150418225</v>
+        <v>0.06495289377313752</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4210895102186915</v>
+        <v>0.4209534094965704</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4350679702616189</v>
+        <v>0.4352037397930689</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02009755319811882</v>
+        <v>0.02012019166013609</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02418677382171767</v>
+        <v>0.02414767606702893</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.01812529140643004</v>
+        <v>0.01810673711623965</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01709869127983898</v>
+        <v>0.01707735176937481</v>
       </c>
       <c r="C42" t="n">
-        <v>0.06676913521840337</v>
+        <v>0.06681810189722813</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4119828006116144</v>
+        <v>0.4118147439449958</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4405487032638252</v>
+        <v>0.4407228138971659</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02107316259898995</v>
+        <v>0.02109786121774564</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02440221562089816</v>
+        <v>0.02436239015725023</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.01877932206028027</v>
+        <v>0.01875951831589232</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01699728253907727</v>
+        <v>0.01697320052413022</v>
       </c>
       <c r="C43" t="n">
-        <v>0.06856893684703637</v>
+        <v>0.06861230543659533</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4018101413984738</v>
+        <v>0.4016106934389755</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4471620363589998</v>
+        <v>0.4473755369784193</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0220657286660398</v>
+        <v>0.02209230401413186</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02461655213009283</v>
+        <v>0.02457644129185542</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.01938052222217564</v>
+        <v>0.01935899444419989</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01693895846445054</v>
+        <v>0.01691202090408981</v>
       </c>
       <c r="C44" t="n">
-        <v>0.07030206649541909</v>
+        <v>0.07033839556846115</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3909850342901575</v>
+        <v>0.3907583695231198</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4545003309120343</v>
+        <v>0.4547508052316122</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02306533610433755</v>
+        <v>0.02309360153815891</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02482775151142542</v>
+        <v>0.02478781279035842</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.01992644397100759</v>
+        <v>0.019902575024255</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01692837632001494</v>
+        <v>0.01689852831745714</v>
       </c>
       <c r="C45" t="n">
-        <v>0.07197352412812599</v>
+        <v>0.07200132464923741</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3799113055640619</v>
+        <v>0.3796644233005935</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4621630977973063</v>
+        <v>0.4624454565745916</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02406330017377325</v>
+        <v>0.0240930361239999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02503395204570991</v>
+        <v>0.02499465600986582</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.02041635574511517</v>
+        <v>0.02038940386312954</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01696755830845541</v>
+        <v>0.01693481668401564</v>
       </c>
       <c r="C46" t="n">
-        <v>0.07358991808191183</v>
+        <v>0.07360765629939046</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3689690201780254</v>
+        <v>0.3687107643108583</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4697712943723503</v>
+        <v>0.4700787614117022</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02505226156524185</v>
+        <v>0.02508318350256822</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0252335917489</v>
+        <v>0.02519541392833543</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.02085110019470477</v>
+        <v>0.02082022495259309</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0170561230826475</v>
+        <v>0.01702058969581947</v>
       </c>
       <c r="C47" t="n">
-        <v>0.07515895160843271</v>
+        <v>0.07516506505263354</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3585024149170739</v>
+        <v>0.3582427878653296</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4769797257059988</v>
+        <v>0.4773045086619204</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02602617992072123</v>
+        <v>0.02605791476499882</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02542550457042102</v>
+        <v>0.02538890900670477</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.02123291379273016</v>
+        <v>0.02119721004573431</v>
       </c>
       <c r="B48" t="n">
-        <v>0.01719160849987186</v>
+        <v>0.01715348380897194</v>
       </c>
       <c r="C48" t="n">
-        <v>0.07668888792173294</v>
+        <v>0.07668182620906847</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3488101103970167</v>
+        <v>0.3485597215306095</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4834872395068424</v>
+        <v>0.4838210273797718</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02698026233911516</v>
+        <v>0.02701233768540547</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02560897754269046</v>
+        <v>0.02557439334043836</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.02156521910261212</v>
+        <v>0.02152375782702352</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01736985328886035</v>
+        <v>0.0173294488303098</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07818803720978054</v>
+        <v>0.07816632985954305</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3401377852729452</v>
+        <v>0.3399072439936224</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4890444781673525</v>
+        <v>0.4893789524001816</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0279108592807827</v>
+        <v>0.02794270588220725</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02578376767766659</v>
+        <v>0.02575156120711225</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.02185240060419255</v>
+        <v>0.02180427437521594</v>
       </c>
       <c r="B50" t="n">
-        <v>0.01758540792403144</v>
+        <v>0.01754315510125158</v>
       </c>
       <c r="C50" t="n">
-        <v>0.07966430512074338</v>
+        <v>0.07962664978215322</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3326733604586161</v>
+        <v>0.3324725097323741</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4934590930735311</v>
+        <v>0.4937865661964307</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02881535121977006</v>
+        <v>0.02884631795418663</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02595008159911526</v>
+        <v>0.02592052685838795</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.02209957475205423</v>
+        <v>0.0220439443847143</v>
       </c>
       <c r="B51" t="n">
-        <v>0.01783194821700884</v>
+        <v>0.01778840114045517</v>
       </c>
       <c r="C51" t="n">
-        <v>0.08112483329182434</v>
+        <v>0.08107019213674112</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3265445847154932</v>
+        <v>0.3263815909543811</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4965984943196716</v>
+        <v>0.4969126778111013</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0296920404617806</v>
+        <v>0.02972141972942582</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02610852424216691</v>
+        <v>0.02608177384318117</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.02231236476682342</v>
+        <v>0.02224850167120536</v>
       </c>
       <c r="B52" t="n">
-        <v>0.01810266902676376</v>
+        <v>0.01805850051026265</v>
       </c>
       <c r="C52" t="n">
-        <v>0.08257575035762654</v>
+        <v>0.08250343508247701</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3218188435214397</v>
+        <v>0.3216993137212612</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4983902952425661</v>
+        <v>0.4986870499739237</v>
       </c>
       <c r="F52" t="n">
-        <v>0.03054005182808744</v>
+        <v>0.03056711400472116</v>
       </c>
       <c r="G52" t="n">
-        <v>0.02626002525669344</v>
+        <v>0.02623608503614918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.0224966878191964</v>
+        <v>0.02242400630022089</v>
       </c>
       <c r="B53" t="n">
-        <v>0.01839064094168116</v>
+        <v>0.0183466316581461</v>
       </c>
       <c r="C53" t="n">
-        <v>0.08402203427133238</v>
+        <v>0.0839317620231443</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3185051074463094</v>
+        <v>0.3184314475628859</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4988205340426936</v>
+        <v>0.4990984133894801</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03135924314197713</v>
+        <v>0.03138327623396425</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02640575233680986</v>
+        <v>0.02638446283215832</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.02265855865024798</v>
+        <v>0.02257663469043263</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01868911859050806</v>
+        <v>0.01864613995709678</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08546747047810187</v>
+        <v>0.08535938194110508</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3165579772686186</v>
+        <v>0.3165291132936885</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4979297329858944</v>
+        <v>0.4981902122677365</v>
       </c>
       <c r="F54" t="n">
-        <v>0.03215012250406529</v>
+        <v>0.03217047125398689</v>
       </c>
       <c r="G54" t="n">
-        <v>0.02654701952256399</v>
+        <v>0.02652804659595335</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.02280391221475131</v>
+        <v>0.02271248816771209</v>
       </c>
       <c r="B55" t="n">
-        <v>0.01899179416070295</v>
+        <v>0.0189507867186886</v>
       </c>
       <c r="C55" t="n">
-        <v>0.08691469106405869</v>
+        <v>0.08678933335945895</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3158836127504062</v>
+        <v>0.3158951133405032</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4958070273399485</v>
+        <v>0.4960543801206215</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03291376539519902</v>
+        <v>0.03292986581535084</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02668519707493298</v>
+        <v>0.02666803247766483</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.02293844658309183</v>
+        <v>0.02283742403216199</v>
       </c>
       <c r="B56" t="n">
-        <v>0.01929299506686123</v>
+        <v>0.0192549446873204</v>
       </c>
       <c r="C56" t="n">
-        <v>0.08836528408941517</v>
+        <v>0.08822357232236369</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3163471182201093</v>
+        <v>0.3163917420484467</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4925828021378889</v>
+        <v>0.4928235843409663</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0336517259843969</v>
+        <v>0.03366313260317805</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0268216279182369</v>
+        <v>0.0268055999655629</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.02306748741118664</v>
+        <v>0.02295691178561916</v>
       </c>
       <c r="B57" t="n">
-        <v>0.01958782874237809</v>
+        <v>0.0195537432160235</v>
       </c>
       <c r="C57" t="n">
-        <v>0.08981996455846804</v>
+        <v>0.08966311322421916</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3177810071677365</v>
+        <v>0.3178495764725785</v>
       </c>
       <c r="E57" t="n">
-        <v>0.488420218995558</v>
+        <v>0.4886624650429039</v>
       </c>
       <c r="F57" t="n">
-        <v>0.03436593795048356</v>
+        <v>0.03437234148365845</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02695755517418913</v>
+        <v>0.02694184877499742</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.02319587510102235</v>
+        <v>0.0230759159529207</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0198722795598204</v>
+        <v>0.01984316836990341</v>
       </c>
       <c r="C58" t="n">
-        <v>0.09127878345418419</v>
+        <v>0.09110818780493142</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3199947030393591</v>
+        <v>0.320076831776677</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4835056953981723</v>
+        <v>0.4837583123716522</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0350585987471782</v>
+        <v>0.03505983506113824</v>
       </c>
       <c r="G58" t="n">
-        <v>0.02709406470026346</v>
+        <v>0.02707774866277708</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.02332787577230558</v>
+        <v>0.02319880558150246</v>
       </c>
       <c r="B59" t="n">
-        <v>0.02014326436605098</v>
+        <v>0.02012012319476686</v>
       </c>
       <c r="C59" t="n">
-        <v>0.09274130908572271</v>
+        <v>0.09255838651735243</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3227851700344915</v>
+        <v>0.3228690445318775</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4780383021297339</v>
+        <v>0.4783114494484003</v>
       </c>
       <c r="F59" t="n">
-        <v>0.03573203429519139</v>
+        <v>0.03572808799095453</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02723204431650391</v>
+        <v>0.02721410273514616</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.02346711806901494</v>
+        <v>0.02332928994692456</v>
       </c>
       <c r="B60" t="n">
-        <v>0.02039865359631809</v>
+        <v>0.02038245191396263</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0942067173540615</v>
+        <v>0.09401276622148451</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3259479614381365</v>
+        <v>0.3260188957742531</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4722188413010624</v>
+        <v>0.4725255183475089</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03638854961695125</v>
+        <v>0.03637955439588188</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02737215862445535</v>
+        <v>0.02735152339998398</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.02361655653471099</v>
+        <v>0.02347038020927768</v>
       </c>
       <c r="B61" t="n">
-        <v>0.02063726250343708</v>
+        <v>0.02062892976785731</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09567381442021315</v>
+        <v>0.09546993702294898</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3292871270472246</v>
+        <v>0.3293257804403321</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4662401219623565</v>
+        <v>0.466598037866979</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0370302804858182</v>
+        <v>0.03701651362108885</v>
       </c>
       <c r="G61" t="n">
-        <v>0.02751483704623935</v>
+        <v>0.02749042107151618</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.02377845926287708</v>
+        <v>0.02362437618693032</v>
       </c>
       <c r="B62" t="n">
-        <v>0.02085881277627567</v>
+        <v>0.02085921927144514</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09714105798342884</v>
+        <v>0.09692813907392335</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3326230165509934</v>
+        <v>0.3326045412023727</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4602793219387126</v>
+        <v>0.4607117918298163</v>
       </c>
       <c r="F62" t="n">
-        <v>0.03765905971045527</v>
+        <v>0.03764092691927751</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02766027177725728</v>
+        <v>0.02763100551623464</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.02395441643024314</v>
+        <v>0.02379287606633562</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0210638638273494</v>
+        <v>0.02107379454391688</v>
       </c>
       <c r="C63" t="n">
-        <v>0.09860659549951972</v>
+        <v>0.09838530295099397</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3357979140541073</v>
+        <v>0.3356927432017615</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4544924819174438</v>
+        <v>0.4550276686965151</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0382763065242678</v>
+        <v>0.0382543171719594</v>
       </c>
       <c r="G63" t="n">
-        <v>0.02780842174706894</v>
+        <v>0.02777329736851724</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.02414536690016102</v>
+        <v>0.02397680638407887</v>
       </c>
       <c r="B64" t="n">
-        <v>0.02125371480523796</v>
+        <v>0.02127383715378971</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1000683026552751</v>
+        <v>0.09983908762069248</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3386796059376548</v>
+        <v>0.3384558440866982</v>
       </c>
       <c r="E64" t="n">
-        <v>0.449011039226773</v>
+        <v>0.449679594167555</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03888294810319252</v>
+        <v>0.0388576833087981</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0279590223717055</v>
+        <v>0.02791714727838777</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.02435164021505341</v>
+        <v>0.0241764698046181</v>
       </c>
       <c r="B65" t="n">
-        <v>0.02143028108451779</v>
+        <v>0.02146110866833182</v>
       </c>
       <c r="C65" t="n">
-        <v>0.101523807118867</v>
+        <v>0.101286899352396</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3411630604358025</v>
+        <v>0.3407898006061565</v>
       </c>
       <c r="E65" t="n">
-        <v>0.443940224848773</v>
+        <v>0.4447720004652319</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03947938296902796</v>
+        <v>0.03945145974022242</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0281116033279585</v>
+        <v>0.02806226136304316</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.02457301095718674</v>
+        <v>0.02439160745360049</v>
       </c>
       <c r="B66" t="n">
-        <v>0.02159595005002505</v>
+        <v>0.02163780588100112</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1029704946946062</v>
+        <v>0.10272589955714</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3431705261344387</v>
+        <v>0.3426212352539082</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4393590105156944</v>
+        <v>0.4403796944458551</v>
       </c>
       <c r="F66" t="n">
-        <v>0.04006549260744477</v>
+        <v>0.04003552707125351</v>
       </c>
       <c r="G66" t="n">
-        <v>0.02826551504060421</v>
+        <v>0.02820823033724167</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.0248087623508359</v>
+        <v>0.02462147111423168</v>
       </c>
       <c r="B67" t="n">
-        <v>0.02175342190104592</v>
+        <v>0.0218064047882093</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1044055029321067</v>
+        <v>0.1041530094105158</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3446503849003656</v>
+        <v>0.3439058266074559</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4353212640038905</v>
+        <v>0.4365494560210944</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04064070180645721</v>
+        <v>0.0406092739969936</v>
       </c>
       <c r="G67" t="n">
-        <v>0.02841996210529819</v>
+        <v>0.0283545580614993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.02505775595495343</v>
+        <v>0.0248649004011341</v>
       </c>
       <c r="B68" t="n">
-        <v>0.02190554254761532</v>
+        <v>0.02196950005898067</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1058257106835412</v>
+        <v>0.1055649175960635</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3455751138480511</v>
+        <v>0.3446256618953135</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4318577536610346</v>
+        <v>0.4333026292774049</v>
       </c>
       <c r="F68" t="n">
-        <v>0.04120408215955847</v>
+        <v>0.04117170408154733</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02857404114524609</v>
+        <v>0.02850068668955578</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.02531850483413189</v>
+        <v>0.02512040118340392</v>
       </c>
       <c r="B69" t="n">
-        <v>0.02205513695838347</v>
+        <v>0.02212964789860508</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1072277328131092</v>
+        <v>0.106958095571937</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3459387366508733</v>
+        <v>0.3447860904753218</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4289786189296986</v>
+        <v>0.4306381699835757</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04175448869379852</v>
+        <v>0.04172157670630934</v>
       </c>
       <c r="G69" t="n">
-        <v>0.02872678112000514</v>
+        <v>0.02864601818084725</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.02558924795207345</v>
+        <v>0.02538622266207161</v>
       </c>
       <c r="B70" t="n">
-        <v>0.02220485188964783</v>
+        <v>0.02228922075118826</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1086079269937239</v>
+        <v>0.1083288228624645</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3457541192678439</v>
+        <v>0.3444124257374163</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4266759532876713</v>
+        <v>0.4285358064650828</v>
       </c>
       <c r="F70" t="n">
-        <v>0.04229071615536886</v>
+        <v>0.04225756856280635</v>
       </c>
       <c r="G70" t="n">
-        <v>0.02887718445367082</v>
+        <v>0.02878993295896995</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.02586802372937549</v>
+        <v>0.02566043119745077</v>
       </c>
       <c r="B71" t="n">
-        <v>0.02235701655853875</v>
+        <v>0.02245028179597163</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1099624178545356</v>
+        <v>0.1096732238076241</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3450503687466481</v>
+        <v>0.3435466916245443</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4249262462939773</v>
+        <v>0.4269591249932707</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0428116595637997</v>
+        <v>0.04277844029217135</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02902426725312517</v>
+        <v>0.02893180628896691</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.02615274103061071</v>
+        <v>0.02594097976834828</v>
       </c>
       <c r="B72" t="n">
-        <v>0.02251352897220882</v>
+        <v>0.02261448599999503</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1112871419866659</v>
+        <v>0.110987317219907</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3438704466800577</v>
+        <v>0.34224446101624</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4236925816400115</v>
+        <v>0.42585854097789</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04331646320782785</v>
+        <v>0.04328319240754201</v>
       </c>
       <c r="G72" t="n">
-        <v>0.02916709648261803</v>
+        <v>0.02907102261007741</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.02644124636313836</v>
+        <v>0.0262257728357478</v>
       </c>
       <c r="B73" t="n">
-        <v>0.02267577401855041</v>
+        <v>0.02278301285307102</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1125779168335339</v>
+        <v>0.1122670810107844</v>
       </c>
       <c r="D73" t="n">
-        <v>0.342268960007022</v>
+        <v>0.3405717362086442</v>
       </c>
       <c r="E73" t="n">
-        <v>0.422926638050083</v>
+        <v>0.4251742136716157</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04380464299153213</v>
+        <v>0.04377119551498166</v>
       </c>
       <c r="G73" t="n">
-        <v>0.02930482173614037</v>
+        <v>0.02920698790515527</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.02673138699562516</v>
+        <v>0.02651272671247491</v>
       </c>
       <c r="B74" t="n">
-        <v>0.02284457762966918</v>
+        <v>0.02295653380741717</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1138305349211934</v>
+        <v>0.1135085341104524</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3403099926409911</v>
+        <v>0.3386018131072873</v>
       </c>
       <c r="E74" t="n">
-        <v>0.422570638791748</v>
+        <v>0.4248389702541621</v>
       </c>
       <c r="F74" t="n">
-        <v>0.04427616948699595</v>
+        <v>0.04424228187986862</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02943669953377757</v>
+        <v>0.02933914012833763</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.02702107020808968</v>
+        <v>0.02679982525680999</v>
       </c>
       <c r="B75" t="n">
-        <v>0.02302019886644606</v>
+        <v>0.02313521489850054</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1150408827762845</v>
+        <v>0.1147078371577972</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3380648191997768</v>
+        <v>0.3364121120449062</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4225594174859748</v>
+        <v>0.4247812645359725</v>
       </c>
       <c r="F75" t="n">
-        <v>0.04473150254559562</v>
+        <v>0.04469678854634537</v>
       </c>
       <c r="G75" t="n">
-        <v>0.02956210891783284</v>
+        <v>0.02946695755966803</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.02730831893364024</v>
+        <v>0.027085170354084</v>
       </c>
       <c r="B76" t="n">
-        <v>0.02320235911125146</v>
+        <v>0.02331875229921484</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1162050806780525</v>
+        <v>0.115861411258652</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3356093820302172</v>
+        <v>0.3340809993589794</v>
       </c>
       <c r="E76" t="n">
-        <v>0.4228227278876112</v>
+        <v>0.4249281551355144</v>
       </c>
       <c r="F76" t="n">
-        <v>0.04517157308585856</v>
+        <v>0.04513554670383445</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0296805582733691</v>
+        <v>0.02958996488972105</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.027591323437214</v>
+        <v>0.02736702649065006</v>
       </c>
       <c r="B77" t="n">
-        <v>0.02339030469654643</v>
+        <v>0.02350643597870993</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1173196361996402</v>
+        <v>0.1169660708323707</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3330214879768148</v>
+        <v>0.3316846539818266</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4232878498756144</v>
+        <v>0.4252082577672151</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04559771330514908</v>
+        <v>0.0455598178072868</v>
       </c>
       <c r="G77" t="n">
-        <v>0.02979168450902092</v>
+        <v>0.02970773714194053</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.02786848774032996</v>
+        <v>0.02764385859429298</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02358289641039853</v>
+        <v>0.02369723444206539</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1183816016074406</v>
+        <v>0.1180191627821259</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3303777855714906</v>
+        <v>0.3292940653743108</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4238824392010813</v>
+        <v>0.4255545932910773</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04601154280748521</v>
+        <v>0.04597118349547106</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02989524666177362</v>
+        <v>0.02981990202065653</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.02813846859230693</v>
+        <v>0.02791436209937078</v>
       </c>
       <c r="B79" t="n">
-        <v>0.02377871683236606</v>
+        <v>0.02388989198112006</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1193887222958099</v>
+        <v>0.1190187008189761</v>
       </c>
       <c r="D79" t="n">
-        <v>0.32775069860217</v>
+        <v>0.3269722854675313</v>
       </c>
       <c r="E79" t="n">
-        <v>0.4245374536336534</v>
+        <v>0.4259072156707396</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04641482378797198</v>
+        <v>0.04637140244843756</v>
       </c>
       <c r="G79" t="n">
-        <v>0.02999111625572179</v>
+        <v>0.02992614151382465</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.02840020434622203</v>
+        <v>0.02817748405135633</v>
       </c>
       <c r="B80" t="n">
-        <v>0.02397618472711121</v>
+        <v>0.02408302922465454</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1203395621855948</v>
+        <v>0.1199634817218613</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3252055653563828</v>
+        <v>0.3247720861212892</v>
       </c>
       <c r="E80" t="n">
-        <v>0.425189914324054</v>
+        <v>0.4262154737557009</v>
       </c>
       <c r="F80" t="n">
-        <v>0.04680930292360889</v>
+        <v>0.04676225167906513</v>
       </c>
       <c r="G80" t="n">
-        <v>0.03007926613702611</v>
+        <v>0.03002619344607242</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.02865293138644808</v>
+        <v>0.02843243419668153</v>
       </c>
       <c r="B81" t="n">
-        <v>0.02417366567886251</v>
+        <v>0.02427523818253693</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1212335919820005</v>
+        <v>0.1208531703802919</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3227982300952489</v>
+        <v>0.3227341842250789</v>
       </c>
       <c r="E81" t="n">
-        <v>0.4257852629752476</v>
+        <v>0.4264397482798261</v>
       </c>
       <c r="F81" t="n">
-        <v>0.04719655928995342</v>
+        <v>0.04714537135682183</v>
       </c>
       <c r="G81" t="n">
-        <v>0.03015975859223887</v>
+        <v>0.03011985337876249</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.02889618671333457</v>
+        <v>0.02867868545446308</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0243695697560483</v>
+        <v>0.02446516446522799</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1220712293160899</v>
+        <v>0.1216883427585162</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3205732757269169</v>
+        <v>0.3208861852847306</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4262791291197214</v>
+        <v>0.4265525142592397</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04757787630394833</v>
+        <v>0.0475221307231664</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03023273306394082</v>
+        <v>0.03020697705465661</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.02912979653450406</v>
+        <v>0.02891596383798537</v>
       </c>
       <c r="B83" t="n">
-        <v>0.02456242980184868</v>
+        <v>0.02465157173214328</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1228538245115738</v>
+        <v>0.1224704799017826</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3185630200206827</v>
+        <v>0.319242362279601</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4266383839370702</v>
+        <v>0.426538610280476</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0479541513608019</v>
+        <v>0.04789352843420557</v>
       </c>
       <c r="G83" t="n">
-        <v>0.03029839383351894</v>
+        <v>0.03028748353380648</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.02935385191688449</v>
+        <v>0.0291442286356697</v>
       </c>
       <c r="B84" t="n">
-        <v>0.02475095719164585</v>
+        <v>0.02483338619504387</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1235835916362026</v>
+        <v>0.1232019109784001</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3167873394008783</v>
+        <v>0.3178043280476197</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4268414109327885</v>
+        <v>0.4263946521253884</v>
       </c>
       <c r="F84" t="n">
-        <v>0.04832585063091832</v>
+        <v>0.04826013490331901</v>
       </c>
       <c r="G84" t="n">
-        <v>0.03035699829068199</v>
+        <v>0.03036135911455923</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.02956867353860306</v>
+        <v>0.0293636443289899</v>
       </c>
       <c r="B85" t="n">
-        <v>0.02493407495570369</v>
+        <v>0.02500972158538984</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1242634905924218</v>
+        <v>0.123885708410234</v>
       </c>
       <c r="D85" t="n">
-        <v>0.3152543248034632</v>
+        <v>0.3165625760450524</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4268775799580162</v>
+        <v>0.4261276094594432</v>
       </c>
       <c r="F85" t="n">
-        <v>0.048693009694456</v>
+        <v>0.04862207824646148</v>
       </c>
       <c r="G85" t="n">
-        <v>0.03040884645733585</v>
+        <v>0.0304286619244292</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.02977476829861855</v>
+        <v>0.02957454621206111</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02511093062252178</v>
+        <v>0.02517988693219813</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1248970712946013</v>
+        <v>0.1245255428302922</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3139617004302269</v>
+        <v>0.3154987629343859</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4267459824444935</v>
+        <v>0.4257526640615349</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0490552746569936</v>
+        <v>0.04897907033390551</v>
       </c>
       <c r="G86" t="n">
-        <v>0.03045427225254446</v>
+        <v>0.030489526695622</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.02997278095430433</v>
+        <v>0.02977740194086933</v>
       </c>
       <c r="B87" t="n">
-        <v>0.02528089269672975</v>
+        <v>0.02534338060470829</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1254882946194458</v>
+        <v>0.1251255094072701</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3128988522680038</v>
+        <v>0.3145885071047863</v>
       </c>
       <c r="E87" t="n">
-        <v>0.4264535685216295</v>
+        <v>0.4252905662509806</v>
       </c>
       <c r="F87" t="n">
-        <v>0.04941197424123007</v>
+        <v>0.04933046582314175</v>
       </c>
       <c r="G87" t="n">
-        <v>0.03049363669865672</v>
+        <v>0.03054416886824381</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.03016344405252706</v>
+        <v>0.02997277130721294</v>
       </c>
       <c r="B88" t="n">
-        <v>0.02544353531212224</v>
+        <v>0.02549987442767196</v>
       </c>
       <c r="C88" t="n">
-        <v>0.126041346083399</v>
+        <v>0.1256899394547492</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3120492402747111</v>
+        <v>0.3138044092051919</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4260128999546224</v>
+        <v>0.4247647736106154</v>
       </c>
       <c r="F88" t="n">
-        <v>0.04976221134433514</v>
+        <v>0.04967534502152762</v>
       </c>
       <c r="G88" t="n">
-        <v>0.03052732297828283</v>
+        <v>0.03059288697303154</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.03034752929635378</v>
+        <v>0.03016126645539175</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0255986154294591</v>
+        <v>0.0256491914951515</v>
       </c>
       <c r="C89" t="n">
-        <v>0.126560457145079</v>
+        <v>0.1262232117761153</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3113929260285828</v>
+        <v>0.313118985033291</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4254397763788205</v>
+        <v>0.4241986721249292</v>
       </c>
       <c r="F89" t="n">
-        <v>0.05010496267085639</v>
+        <v>0.05001261081299882</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03055573305084851</v>
+        <v>0.03063606230212238</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.03052580314913517</v>
+        <v>0.03034351456431825</v>
       </c>
       <c r="B90" t="n">
-        <v>0.02574604629469727</v>
+        <v>0.02579128083182534</v>
       </c>
       <c r="C90" t="n">
-        <v>0.1270497457010965</v>
+        <v>0.1267295768427083</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3109089458599328</v>
+        <v>0.312507236218456</v>
       </c>
       <c r="E90" t="n">
-        <v>0.4247509971524173</v>
+        <v>0.4236131460557422</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0504391764304627</v>
+        <v>0.05034109034016543</v>
       </c>
       <c r="G90" t="n">
-        <v>0.03057928541225829</v>
+        <v>0.03067415514678465</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.03069898895003011</v>
+        <v>0.03052012469967012</v>
       </c>
       <c r="B91" t="n">
-        <v>0.02588586995325744</v>
+        <v>0.02592619146242461</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1275130835162151</v>
+        <v>0.1272130041342307</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3105772963130453</v>
+        <v>0.3119486518264127</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4239624872758198</v>
+        <v>0.4230246972853235</v>
       </c>
       <c r="F91" t="n">
-        <v>0.05076386044690745</v>
+        <v>0.05065963329070963</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03059841354472491</v>
+        <v>0.03070769730122881</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.03086773705098454</v>
+        <v>0.03069166010265791</v>
       </c>
       <c r="B92" t="n">
-        <v>0.02601823071369458</v>
+        <v>0.02605404785319951</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1279539943491743</v>
+        <v>0.1276770595937848</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3103803663211739</v>
+        <v>0.3114285151364374</v>
       </c>
       <c r="E92" t="n">
-        <v>0.4230879516195942</v>
+        <v>0.4224442361218783</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05107815531183428</v>
+        <v>0.05096720016113387</v>
       </c>
       <c r="G92" t="n">
-        <v>0.03061356463354454</v>
+        <v>0.03073728103090811</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.03103260370700176</v>
+        <v>0.03085861667713375</v>
       </c>
       <c r="B93" t="n">
-        <v>0.02614335070665226</v>
+        <v>0.02617502814164028</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1283755836968312</v>
+        <v>0.1281248169149797</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3103037369216681</v>
+        <v>0.3109384728155713</v>
       </c>
       <c r="E93" t="n">
-        <v>0.4221381372297706</v>
+        <v>0.4218765847834717</v>
       </c>
       <c r="F93" t="n">
-        <v>0.05138138949580282</v>
+        <v>0.05126293550191578</v>
       </c>
       <c r="G93" t="n">
-        <v>0.03062519824227342</v>
+        <v>0.0307635451652879</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.03119403866228493</v>
+        <v>0.03102140796206547</v>
       </c>
       <c r="B94" t="n">
-        <v>0.02626150811751968</v>
+        <v>0.02628934612363396</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1287804991618588</v>
+        <v>0.1285588036972093</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3103363611637734</v>
+        <v>0.3104764026289807</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4211206930060805</v>
+        <v>0.4213206576355839</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05167311515033277</v>
+        <v>0.05154622271296914</v>
       </c>
       <c r="G94" t="n">
-        <v>0.03063378473814956</v>
+        <v>0.03078715923955777</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.03135238074408313</v>
+        <v>0.03118035647458602</v>
       </c>
       <c r="B95" t="n">
-        <v>0.02637301834366372</v>
+        <v>0.02639723758095579</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1291709189836567</v>
+        <v>0.1289809814264309</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3104702193047786</v>
+        <v>0.3100456852753333</v>
       </c>
       <c r="E95" t="n">
-        <v>0.4200405344505234</v>
+        <v>0.42077021417178</v>
       </c>
       <c r="F95" t="n">
-        <v>0.05195312479451422</v>
+        <v>0.05181671840413529</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0306398033787803</v>
+        <v>0.03080880666677884</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.03150786030092557</v>
+        <v>0.03133569094758994</v>
       </c>
       <c r="B96" t="n">
-        <v>0.02647821816164667</v>
+        <v>0.0264989509697898</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1295485653847855</v>
+        <v>0.1293927566242557</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3106996046086233</v>
+        <v>0.3096540385389375</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4189005612624326</v>
+        <v>0.4202150291680756</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05222145026809717</v>
+        <v>0.05207436582067741</v>
       </c>
       <c r="G96" t="n">
-        <v>0.03064374001348931</v>
+        <v>0.03082916793067407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.03166060706856821</v>
+        <v>0.03148754868608786</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0265774529313399</v>
+        <v>0.02659474164165847</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1299147387546812</v>
+        <v>0.1297950192426511</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3110202232644267</v>
+        <v>0.3093120999730347</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4177025474095212</v>
+        <v>0.4196422971613824</v>
       </c>
       <c r="F97" t="n">
-        <v>0.05247834621555754</v>
+        <v>0.05231938852928399</v>
       </c>
       <c r="G97" t="n">
-        <v>0.03064608435590508</v>
+        <v>0.03084890476590141</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.0318106619608007</v>
+        <v>0.03163598208469515</v>
       </c>
       <c r="B98" t="n">
-        <v>0.02667106681470908</v>
+        <v>0.0266848682456687</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1302703681494529</v>
+        <v>0.1301882034080276</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3114282862235604</v>
+        <v>0.3090319436050216</v>
       </c>
       <c r="E98" t="n">
-        <v>0.4164480290470665</v>
+        <v>0.4190380895038107</v>
       </c>
       <c r="F98" t="n">
-        <v>0.05272426105031847</v>
+        <v>0.05255226700297136</v>
       </c>
       <c r="G98" t="n">
-        <v>0.03064732675409199</v>
+        <v>0.03086864614980485</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.03195799131819532</v>
+        <v>0.0317809682879625</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0267593958655863</v>
+        <v>0.02676959045419941</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1306160733598981</v>
+        <v>0.1305723648754328</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3119197353132133</v>
+        <v>0.3088256891173458</v>
       </c>
       <c r="E99" t="n">
-        <v>0.4151390509291599</v>
+        <v>0.4183887092804042</v>
       </c>
       <c r="F99" t="n">
-        <v>0.052959798846213</v>
+        <v>0.05277370132507501</v>
       </c>
       <c r="G99" t="n">
-        <v>0.03064795436773395</v>
+        <v>0.03088897665958019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.0321025022851946</v>
+        <v>0.03192242098497113</v>
       </c>
       <c r="B100" t="n">
-        <v>0.02684276367493571</v>
+        <v>0.02684916782316767</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1309522337150828</v>
+        <v>0.130947268983408</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3124896915823188</v>
+        <v>0.3087043173937158</v>
       </c>
       <c r="E100" t="n">
-        <v>0.4137786860661681</v>
+        <v>0.4176818337428047</v>
       </c>
       <c r="F100" t="n">
-        <v>0.05318567597476052</v>
+        <v>0.05298456366040667</v>
       </c>
       <c r="G100" t="n">
-        <v>0.03064844670153941</v>
+        <v>0.03091042741152595</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.03224405817126774</v>
+        <v>0.03206020336321395</v>
       </c>
       <c r="B101" t="n">
-        <v>0.02692147908987163</v>
+        <v>0.02692385944454957</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1312790586978068</v>
+        <v>0.1313124825432403</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3131321541057253</v>
+        <v>0.3086767559411283</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4123713029798432</v>
+        <v>0.4169073840818676</v>
       </c>
       <c r="F101" t="n">
-        <v>0.05340267643282677</v>
+        <v>0.05318584510645151</v>
       </c>
       <c r="G101" t="n">
-        <v>0.03064927052265881</v>
+        <v>0.0309334695195489</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.03238249287485581</v>
+        <v>0.0321941413115447</v>
       </c>
       <c r="B102" t="n">
-        <v>0.02699583541633362</v>
+        <v>0.0269939237013427</v>
       </c>
       <c r="C102" t="n">
-        <v>0.131596655640253</v>
+        <v>0.1316674631174489</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3138399248736409</v>
+        <v>0.3087492520373311</v>
       </c>
       <c r="E102" t="n">
-        <v>0.4109226072806464</v>
+        <v>0.4160581078053164</v>
       </c>
       <c r="F102" t="n">
-        <v>0.05361160963967002</v>
+        <v>0.05337860215400214</v>
       </c>
       <c r="G102" t="n">
-        <v>0.03065087427460012</v>
+        <v>0.03095850987301421</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.03251762367243819</v>
+        <v>0.03232403608900234</v>
       </c>
       <c r="B103" t="n">
-        <v>0.02706611050965487</v>
+        <v>0.027059617535939</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1319050899268733</v>
+        <v>0.1320116397056866</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3146047003837286</v>
+        <v>0.3089250172839703</v>
       </c>
       <c r="E103" t="n">
-        <v>0.4094395194448766</v>
+        <v>0.4151298928803746</v>
       </c>
       <c r="F103" t="n">
-        <v>0.05381327388849615</v>
+        <v>0.05356390751363142</v>
       </c>
       <c r="G103" t="n">
-        <v>0.03065368217393265</v>
+        <v>0.03098588899139589</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.03264926192746644</v>
+        <v>0.0324496758713967</v>
       </c>
       <c r="B104" t="n">
-        <v>0.02713256721354147</v>
+        <v>0.02712119499808124</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1322044338971087</v>
+        <v>0.1323444799889996</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3154172565175403</v>
+        <v>0.3092041068265854</v>
       </c>
       <c r="E104" t="n">
-        <v>0.4079299643971079</v>
+        <v>0.414121852856684</v>
       </c>
       <c r="F104" t="n">
-        <v>0.05400842783430997</v>
+        <v>0.05374280877839761</v>
       </c>
       <c r="G104" t="n">
-        <v>0.03065808821292545</v>
+        <v>0.03101588067985553</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.03277722149808745</v>
+        <v>0.03257084582023678</v>
       </c>
       <c r="B105" t="n">
-        <v>0.02719545376644523</v>
+        <v>0.0271789051804568</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1324948014117368</v>
+        <v>0.13266554083788</v>
       </c>
       <c r="D105" t="n">
-        <v>0.3162676598043098</v>
+        <v>0.3095834883451227</v>
       </c>
       <c r="E105" t="n">
-        <v>0.406402641982633</v>
+        <v>0.4130362298466482</v>
       </c>
       <c r="F105" t="n">
-        <v>0.05419777121049903</v>
+        <v>0.05391629681126285</v>
       </c>
       <c r="G105" t="n">
-        <v>0.03066445032628881</v>
+        <v>0.03104869315839274</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.03290132485835632</v>
+        <v>0.03268733654752958</v>
       </c>
       <c r="B106" t="n">
-        <v>0.02725500394442101</v>
+        <v>0.0272329898867062</v>
       </c>
       <c r="C106" t="n">
-        <v>0.132776366590783</v>
+        <v>0.1329745005371447</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3171454577947972</v>
+        <v>0.310057256438925</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4048668269312234</v>
+        <v>0.4118781610467299</v>
       </c>
       <c r="F106" t="n">
-        <v>0.05438193489809768</v>
+        <v>0.0540852842484786</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0306730849823211</v>
+        <v>0.03108447129448623</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.03302140713196392</v>
+        <v>0.03279895104441363</v>
       </c>
       <c r="B107" t="n">
-        <v>0.0273114368831962</v>
+        <v>0.02728368147230647</v>
       </c>
       <c r="C107" t="n">
-        <v>0.133049366677377</v>
+        <v>0.13327117291495</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3180398266269869</v>
+        <v>0.3106169532784325</v>
       </c>
       <c r="E107" t="n">
-        <v>0.403332220848618</v>
+        <v>0.4106553483804938</v>
       </c>
       <c r="F107" t="n">
-        <v>0.05456147938016197</v>
+        <v>0.05425059332859172</v>
       </c>
       <c r="G107" t="n">
-        <v>0.030684262451696</v>
+        <v>0.03112329958081182</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.03313731841028231</v>
+        <v>0.03290551028553623</v>
       </c>
       <c r="B108" t="n">
-        <v>0.0273649566562807</v>
+        <v>0.02733120124672612</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1333140906855568</v>
+        <v>0.1335555051334145</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3189396765130973</v>
+        <v>0.3112519632360632</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4018088548399409</v>
+        <v>0.4093776630307179</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05473689990533683</v>
+        <v>0.05441295147714249</v>
       </c>
       <c r="G108" t="n">
-        <v>0.030698202989505</v>
+        <v>0.03116520559039965</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.03324892484611244</v>
+        <v>0.0330068578068583</v>
       </c>
       <c r="B109" t="n">
-        <v>0.02741575178496023</v>
+        <v>0.02737575866519644</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1335708568485173</v>
+        <v>0.1338275621891283</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3198337316266451</v>
+        <v>0.3119499557713877</v>
       </c>
       <c r="E109" t="n">
-        <v>0.4003070245418399</v>
+        <v>0.4080567090988552</v>
       </c>
       <c r="F109" t="n">
-        <v>0.05490863621165604</v>
+        <v>0.05457299267945968</v>
       </c>
       <c r="G109" t="n">
-        <v>0.03071507414026877</v>
+        <v>0.03121016378911434</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.0333561090833378</v>
+        <v>0.03310286358179949</v>
       </c>
       <c r="B110" t="n">
-        <v>0.02746399490808962</v>
+        <v>0.02741755134378685</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1338199829314656</v>
+        <v>0.134087502077466</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3207106077416867</v>
+        <v>0.3126973563891707</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3988372314179894</v>
+        <v>0.4067053642869422</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05507708457533795</v>
+        <v>0.05473126258993077</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0307349893420926</v>
+        <v>0.0312580997309042</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.0334587705826238</v>
+        <v>0.03319342749655133</v>
       </c>
       <c r="B111" t="n">
-        <v>0.02750984282611652</v>
+        <v>0.02745676577179221</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1340617538979971</v>
+        <v>0.1343355460011759</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3215589108265142</v>
+        <v>0.3134798299545355</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3974101039038603</v>
+        <v>0.4053373105512044</v>
       </c>
       <c r="F111" t="n">
-        <v>0.05524261001161122</v>
+        <v>0.05488822547757452</v>
       </c>
       <c r="G111" t="n">
-        <v>0.03075800795127702</v>
+        <v>0.03130889474716624</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.03355682635297507</v>
+        <v>0.03327848266181168</v>
       </c>
       <c r="B112" t="n">
-        <v>0.02755343708092544</v>
+        <v>0.02749357850365514</v>
       </c>
       <c r="C112" t="n">
-        <v>0.134296391386744</v>
+        <v>0.1345719479068114</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3223673751499452</v>
+        <v>0.3142827642012505</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3960362765494481</v>
+        <v>0.4039665640633499</v>
       </c>
       <c r="F112" t="n">
-        <v>0.05540555673132194</v>
+        <v>0.05504427142104994</v>
       </c>
       <c r="G112" t="n">
-        <v>0.03078413674863999</v>
+        <v>0.03136239124207139</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.03365021248298072</v>
+        <v>0.03335799870879844</v>
       </c>
       <c r="B113" t="n">
-        <v>0.02759490513532236</v>
+        <v>0.02752815758634825</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1345240288997582</v>
+        <v>0.1347969670499691</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3231250533675495</v>
+        <v>0.3150917439828244</v>
       </c>
       <c r="E113" t="n">
-        <v>0.3947262119145691</v>
+        <v>0.4026070114699392</v>
       </c>
       <c r="F113" t="n">
-        <v>0.05556625529717396</v>
+        <v>0.05519972256825561</v>
       </c>
       <c r="G113" t="n">
-        <v>0.03081333290264605</v>
+        <v>0.03141839863386514</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.03373888671968769</v>
+        <v>0.03343198511460737</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0276343621019936</v>
+        <v>0.02756066399442855</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1347446956634161</v>
+        <v>0.1350108463422965</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3238215650595258</v>
+        <v>0.3158930085878698</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3934899568179757</v>
+        <v>0.4012719583916569</v>
       </c>
       <c r="F114" t="n">
-        <v>0.05572502536268096</v>
+        <v>0.05535483769777005</v>
       </c>
       <c r="G114" t="n">
-        <v>0.03084550827472029</v>
+        <v>0.03147669987137078</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.03382283216623167</v>
+        <v>0.03350049449975134</v>
       </c>
       <c r="B115" t="n">
-        <v>0.02767191286594074</v>
+        <v>0.02759125288019055</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1349583109019535</v>
+        <v>0.1352137981018008</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3244474044777586</v>
+        <v>0.3166738850321755</v>
       </c>
       <c r="E115" t="n">
-        <v>0.3923368313535993</v>
+        <v>0.399973696434589</v>
       </c>
       <c r="F115" t="n">
-        <v>0.05588217337874134</v>
+        <v>0.0555098147099084</v>
       </c>
       <c r="G115" t="n">
-        <v>0.03088053485577451</v>
+        <v>0.03153705834158396</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.03390206199495827</v>
+        <v>0.03356362575057718</v>
       </c>
       <c r="B116" t="n">
-        <v>0.02770765437282675</v>
+        <v>0.02762007448259967</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1351646889759378</v>
+        <v>0.1354059977036771</v>
       </c>
       <c r="D116" t="n">
-        <v>0.324994302081992</v>
+        <v>0.3174231894892254</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3912750563147193</v>
+        <v>0.3987230966682895</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05603798521383584</v>
+        <v>0.05566479100904806</v>
       </c>
       <c r="G116" t="n">
-        <v>0.03091825104572986</v>
+        <v>0.03159922489658265</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.03397662490545966</v>
+        <v>0.03362152675237629</v>
       </c>
       <c r="B117" t="n">
-        <v>0.02774167783005287</v>
+        <v>0.02764727456919274</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1353635546043091</v>
+        <v>0.1355875846723876</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3254556268701367</v>
+        <v>0.3181315870693626</v>
       </c>
       <c r="E117" t="n">
-        <v>0.3903113331873693</v>
+        <v>0.3975292402405036</v>
       </c>
       <c r="F117" t="n">
-        <v>0.05619271416879778</v>
+        <v>0.05581984201396575</v>
       </c>
       <c r="G117" t="n">
-        <v>0.03095846843387495</v>
+        <v>0.03166294468221122</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.03404661092151377</v>
+        <v>0.0336743964824095</v>
       </c>
       <c r="B118" t="n">
-        <v>0.02777407057129803</v>
+        <v>0.02767299431601434</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1355545665491162</v>
+        <v>0.1357586700767371</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3258268078416809</v>
+        <v>0.3187918976260178</v>
       </c>
       <c r="E118" t="n">
-        <v>0.3894503999858122</v>
+        <v>0.3963990997998739</v>
       </c>
       <c r="F118" t="n">
-        <v>0.05634656542554628</v>
+        <v>0.05597497825047452</v>
       </c>
       <c r="G118" t="n">
-        <v>0.03100097870503234</v>
+        <v>0.03172796344847272</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.03411215701612183</v>
+        <v>0.03372248620798665</v>
       </c>
       <c r="B119" t="n">
-        <v>0.02780491740074151</v>
+        <v>0.02769736957464139</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1357373473980355</v>
+        <v>0.1359193487315234</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3261057443599985</v>
+        <v>0.3193993332328764</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3886945951296598</v>
+        <v>0.3953372875626801</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05649967838431856</v>
+        <v>0.05613014163762695</v>
       </c>
       <c r="G119" t="n">
-        <v>0.03104556031112389</v>
+        <v>0.03179403305266525</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.03417345199584486</v>
+        <v>0.0337660995582564</v>
       </c>
       <c r="B120" t="n">
-        <v>0.02783430129548291</v>
+        <v>0.02772052954222274</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1359115168762431</v>
+        <v>0.136069714649662</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3262931684267372</v>
+        <v>0.3199516526829605</v>
       </c>
       <c r="E120" t="n">
-        <v>0.388043468153095</v>
+        <v>0.3943458859776342</v>
       </c>
       <c r="F120" t="n">
-        <v>0.05665210868006788</v>
+        <v>0.05628520167102186</v>
       </c>
       <c r="G120" t="n">
-        <v>0.03109198457252892</v>
+        <v>0.03186091591824208</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.03423074006210558</v>
+        <v>0.03380559127836393</v>
       </c>
       <c r="B121" t="n">
-        <v>0.02786230342852998</v>
+        <v>0.02774259493831448</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1360767260737515</v>
+        <v>0.1362098783459048</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3263929190440379</v>
+        <v>0.3204492207144054</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3874934785991633</v>
+        <v>0.3934243742113158</v>
       </c>
       <c r="F121" t="n">
-        <v>0.05680381185995762</v>
+        <v>0.05643995223585812</v>
       </c>
       <c r="G121" t="n">
-        <v>0.03114002093245406</v>
+        <v>0.03192838827583743</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.03428432250007604</v>
+        <v>0.03384136452009135</v>
       </c>
       <c r="B122" t="n">
-        <v>0.0278890025536346</v>
+        <v>0.02776367588843454</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1362326901854975</v>
+        <v>0.136339984850662</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3264120909687312</v>
+        <v>0.3208949647416362</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3870378219480884</v>
+        <v>0.3925696581569496</v>
       </c>
       <c r="F122" t="n">
-        <v>0.05695463067962656</v>
+        <v>0.05659410975849435</v>
       </c>
       <c r="G122" t="n">
-        <v>0.03118944116434582</v>
+        <v>0.03199624208373208</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.03433455702984722</v>
+        <v>0.03387386656744267</v>
       </c>
       <c r="B123" t="n">
-        <v>0.02791447386254747</v>
+        <v>0.02778386979759242</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1363792177109559</v>
+        <v>0.1364602315291052</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3263610278983601</v>
+        <v>0.3212942286992458</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3866664132924466</v>
+        <v>0.391776204461904</v>
       </c>
       <c r="F123" t="n">
-        <v>0.05710428778125926</v>
+        <v>0.05674731334231647</v>
       </c>
       <c r="G123" t="n">
-        <v>0.03124002242458354</v>
+        <v>0.03206428560239358</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.03438185448061177</v>
+        <v>0.03390358294054846</v>
       </c>
       <c r="B124" t="n">
-        <v>0.02793878748217239</v>
+        <v>0.02780325954568953</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1365162345285324</v>
+        <v>0.1365708849217638</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3262531424183026</v>
+        <v>0.3216545305081746</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3863660468623387</v>
+        <v>0.3910362719600355</v>
       </c>
       <c r="F124" t="n">
-        <v>0.05725238508803155</v>
+        <v>0.05689912744146382</v>
       </c>
       <c r="G124" t="n">
-        <v>0.03129154914001064</v>
+        <v>0.03213234268232482</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.03442667262465036</v>
+        <v>0.03393102987386474</v>
       </c>
       <c r="B125" t="n">
-        <v>0.02796200682500656</v>
+        <v>0.02782191233330129</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1366438016650572</v>
+        <v>0.1366722957956395</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3261045604201424</v>
+        <v>0.3219852349630617</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3861207339714422</v>
+        <v>0.3903402286130263</v>
       </c>
       <c r="F125" t="n">
-        <v>0.05739841067394232</v>
+        <v>0.05704904750539585</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0313438138197594</v>
+        <v>0.03220025091571042</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.0344695072096949</v>
+        <v>0.03395674523192523</v>
       </c>
       <c r="B126" t="n">
-        <v>0.02798418703334887</v>
+        <v>0.02783987944477713</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1367621260581626</v>
+        <v>0.1367649114520801</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3259336032612324</v>
+        <v>0.322297156615149</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3859122063090189</v>
+        <v>0.3896769394936253</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0575417531648447</v>
+        <v>0.05719650886680804</v>
       </c>
       <c r="G126" t="n">
-        <v>0.03139661696369745</v>
+        <v>0.03226785889563544</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.03451088044878953</v>
+        <v>0.03398127801076397</v>
       </c>
       <c r="B127" t="n">
-        <v>0.02800537376648588</v>
+        <v>0.02785719708454868</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1368715639380733</v>
+        <v>0.136849284174697</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3257601344176456</v>
+        <v>0.3226021077193538</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3857205581039654</v>
+        <v>0.3890342111658805</v>
       </c>
       <c r="F127" t="n">
-        <v>0.05768172301719122</v>
+        <v>0.05734089893275082</v>
       </c>
       <c r="G127" t="n">
-        <v>0.03144976630784931</v>
+        <v>0.03233502291200536</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.03455132743901648</v>
+        <v>0.03400517667192856</v>
       </c>
       <c r="B128" t="n">
-        <v>0.02802560255662425</v>
+        <v>0.02787388830368199</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1369726167717306</v>
+        <v>0.1369260746394956</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3256048069222428</v>
+        <v>0.3229124056817496</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3855249912270496</v>
+        <v>0.3883992787528694</v>
       </c>
       <c r="F128" t="n">
-        <v>0.05781757939313901</v>
+        <v>0.05748157247348019</v>
       </c>
       <c r="G128" t="n">
-        <v>0.03150307569019747</v>
+        <v>0.03240160347679482</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.03459138115239881</v>
+        <v>0.03402897665888032</v>
       </c>
       <c r="B129" t="n">
-        <v>0.02804489890054673</v>
+        <v>0.02788996589297367</v>
       </c>
       <c r="C129" t="n">
-        <v>0.137065920047485</v>
+        <v>0.1369960492460818</v>
       </c>
       <c r="D129" t="n">
-        <v>0.325488252815251</v>
+        <v>0.3232403541010557</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3853046223883952</v>
+        <v>0.3877593224945654</v>
       </c>
       <c r="F129" t="n">
-        <v>0.05794856086013641</v>
+        <v>0.05761786950660491</v>
       </c>
       <c r="G129" t="n">
-        <v>0.03155636383578668</v>
+        <v>0.03246746209983832</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.034631556769417</v>
+        <v>0.03405318754027053</v>
       </c>
       <c r="B130" t="n">
-        <v>0.02806327917402398</v>
+        <v>0.0279054359989601</v>
       </c>
       <c r="C130" t="n">
-        <v>0.13715222536778</v>
+        <v>0.137060070701701</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3254302570293428</v>
+        <v>0.3235977124174741</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3850393104444854</v>
+        <v>0.3871019996267101</v>
       </c>
       <c r="F130" t="n">
-        <v>0.05807391785127684</v>
+        <v>0.05774913499158622</v>
       </c>
       <c r="G130" t="n">
-        <v>0.03160945336367402</v>
+        <v>0.03253245872329816</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.03467233617300438</v>
+        <v>0.0340782802973964</v>
       </c>
       <c r="B131" t="n">
-        <v>0.02808075233834445</v>
+        <v>0.02792030213410525</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1372323767429676</v>
+        <v>0.1371190817582868</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3254489564746762</v>
+        <v>0.323995171488625</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3847104632527999</v>
+        <v>0.386415974820309</v>
       </c>
       <c r="F131" t="n">
-        <v>0.05819294473640758</v>
+        <v>0.05787473933318005</v>
       </c>
       <c r="G131" t="n">
-        <v>0.03166217028179956</v>
+        <v>0.03259645016809731</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.03471415341375615</v>
+        <v>0.03410467531410021</v>
       </c>
       <c r="B132" t="n">
-        <v>0.02809732231345959</v>
+        <v>0.02793456920910438</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1373072822378716</v>
+        <v>0.1371740826712016</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3255601018034965</v>
+        <v>0.3244418554238416</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3843017865713281</v>
+        <v>0.3856914289398233</v>
       </c>
       <c r="F132" t="n">
-        <v>0.05830500946398037</v>
+        <v>0.05799409858673359</v>
       </c>
       <c r="G132" t="n">
-        <v>0.03171434419610759</v>
+        <v>0.03265928985519539</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.03475738187370585</v>
+        <v>0.03413273162860746</v>
       </c>
       <c r="B133" t="n">
-        <v>0.02811299079586437</v>
+        <v>0.02794824721434138</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1373778825034851</v>
+        <v>0.137226103596729</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3257764150820584</v>
+        <v>0.3249448726272288</v>
       </c>
       <c r="E133" t="n">
-        <v>0.383799941349021</v>
+        <v>0.3849205227062489</v>
       </c>
       <c r="F133" t="n">
-        <v>0.05840957901805773</v>
+        <v>0.05810669327936804</v>
       </c>
       <c r="G133" t="n">
-        <v>0.03176580937780751</v>
+        <v>0.03272082894747644</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.03480232374358542</v>
+        <v>0.03416273796673772</v>
       </c>
       <c r="B134" t="n">
-        <v>0.02812776026298201</v>
+        <v>0.02796135421748197</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1374451179207723</v>
+        <v>0.1372761736679335</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3261070715872753</v>
+        <v>0.3255089401319886</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3831950803734444</v>
+        <v>0.3840977901913059</v>
       </c>
       <c r="F134" t="n">
-        <v>0.05850623935640802</v>
+        <v>0.05821208489860375</v>
       </c>
       <c r="G134" t="n">
-        <v>0.03181640675553263</v>
+        <v>0.03278091892594857</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.034849202263656</v>
+        <v>0.0341949059963713</v>
       </c>
       <c r="B135" t="n">
-        <v>0.02814163688557853</v>
+        <v>0.02797391841973377</v>
       </c>
       <c r="C135" t="n">
-        <v>0.137509896252262</v>
+        <v>0.1373252888105937</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3265573280776545</v>
+        <v>0.3261361042213703</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3824812407419257</v>
+        <v>0.3832204377534447</v>
       </c>
       <c r="F135" t="n">
-        <v>0.05859470899330241</v>
+        <v>0.05830992931992234</v>
       </c>
       <c r="G135" t="n">
-        <v>0.03186598678562059</v>
+        <v>0.03283941547856362</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.03489815701146477</v>
+        <v>0.03422936613019506</v>
       </c>
       <c r="B136" t="n">
-        <v>0.02815463310620353</v>
+        <v>0.0279859791157908</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1375730626749273</v>
+        <v>0.1373743804465849</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3271283131016154</v>
+        <v>0.3268255767550323</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3816565751355483</v>
+        <v>0.3822885273960171</v>
       </c>
       <c r="F136" t="n">
-        <v>0.05867484591189884</v>
+        <v>0.05839998670338962</v>
       </c>
       <c r="G136" t="n">
-        <v>0.03191441305834209</v>
+        <v>0.03289618345299015</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0.03494924233597475</v>
+        <v>0.03426616606757443</v>
       </c>
       <c r="B137" t="n">
-        <v>0.02816676969914352</v>
+        <v>0.02799758652046013</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1376353738402746</v>
+        <v>0.1374242870831317</v>
       </c>
       <c r="D137" t="n">
-        <v>0.3278169870313756</v>
+        <v>0.3275737007526205</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3807234127289936</v>
+        <v>0.3813050294110774</v>
       </c>
       <c r="F137" t="n">
-        <v>0.05874664796626203</v>
+        <v>0.05848212764657714</v>
       </c>
       <c r="G137" t="n">
-        <v>0.03196156639797606</v>
+        <v>0.03295110251855887</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.03500242887036362</v>
+        <v>0.03430527211752513</v>
       </c>
       <c r="B138" t="n">
-        <v>0.02817807719342682</v>
+        <v>0.02800880054362025</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1376974773298775</v>
+        <v>0.1374757304363949</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3286162712175454</v>
+        <v>0.3283740511765848</v>
       </c>
       <c r="E138" t="n">
-        <v>0.379688148901529</v>
+        <v>0.3802757370165205</v>
       </c>
       <c r="F138" t="n">
-        <v>0.05881024734931493</v>
+        <v>0.05855633560314205</v>
       </c>
       <c r="G138" t="n">
-        <v>0.03200734913794263</v>
+        <v>0.03300407310621244</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.03505760790878732</v>
+        <v>0.03434657319646654</v>
       </c>
       <c r="B139" t="n">
-        <v>0.02818859664240799</v>
+        <v>0.02801968870111614</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1377598972741853</v>
+        <v>0.1375292972509128</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3295153368872851</v>
+        <v>0.3292176682662064</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3785609720888271</v>
+        <v>0.3792090446828422</v>
       </c>
       <c r="F139" t="n">
-        <v>0.05886589997916924</v>
+        <v>0.05862270574600651</v>
       </c>
       <c r="G139" t="n">
-        <v>0.03205168921933827</v>
+        <v>0.03305502215644936</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.03511459828919548</v>
+        <v>0.0343898872579055</v>
       </c>
       <c r="B140" t="n">
-        <v>0.02819837974895549</v>
+        <v>0.02803032343003981</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1378230265649456</v>
+        <v>0.1375854274324322</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3305000369244529</v>
+        <v>0.3300934120366724</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3773554438675529</v>
+        <v>0.3781156010732269</v>
       </c>
       <c r="F140" t="n">
-        <v>0.05891397088304971</v>
+        <v>0.05868144056356409</v>
       </c>
       <c r="G140" t="n">
-        <v>0.03209454372184768</v>
+        <v>0.0331039082061591</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.0351731553461588</v>
+        <v>0.03443496979717232</v>
       </c>
       <c r="B141" t="n">
-        <v>0.02820748844725157</v>
+        <v>0.02804077912495156</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1378871254160622</v>
+        <v>0.1376444085947515</v>
       </c>
       <c r="D141" t="n">
-        <v>0.3315534566358637</v>
+        <v>0.3309884184667735</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3760879559602932</v>
+        <v>0.3770078560976128</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0589549167076924</v>
+        <v>0.05873284253437056</v>
       </c>
       <c r="G141" t="n">
-        <v>0.03213590148667848</v>
+        <v>0.03315072538436786</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.03523298142288002</v>
+        <v>0.03448152398962221</v>
       </c>
       <c r="B142" t="n">
-        <v>0.02821599404927806</v>
+        <v>0.02805112922280591</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1379523257124594</v>
+        <v>0.1377063766935483</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3326565547757331</v>
+        <v>0.3318886311739224</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3747770930091549</v>
+        <v>0.3758995287156083</v>
       </c>
       <c r="F142" t="n">
-        <v>0.05898926650015261</v>
+        <v>0.05877730424557259</v>
       </c>
       <c r="G142" t="n">
-        <v>0.03217578453034206</v>
+        <v>0.03319550595892028</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.03529373740441492</v>
+        <v>0.03452921196942913</v>
       </c>
       <c r="B143" t="n">
-        <v>0.02822397608248893</v>
+        <v>0.02806144363845543</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1380186402548946</v>
+        <v>0.1377713221132609</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3337888627806451</v>
+        <v>0.3327793776292377</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3734429336281065</v>
+        <v>0.3748050271492207</v>
       </c>
       <c r="F143" t="n">
-        <v>0.05901760181417678</v>
+        <v>0.05881529632711631</v>
       </c>
       <c r="G143" t="n">
-        <v>0.03221424803527324</v>
+        <v>0.03323832117328</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.03535505473655284</v>
+        <v>0.03457766673784625</v>
       </c>
       <c r="B144" t="n">
-        <v>0.02823152093684847</v>
+        <v>0.0280717867932133</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1380859758811232</v>
+        <v>0.1378391003832496</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3349292087441683</v>
+        <v>0.3336459566606758</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3721063238377264</v>
+        <v>0.3737388556097291</v>
       </c>
       <c r="F144" t="n">
-        <v>0.05904053706112307</v>
+        <v>0.05884735358863098</v>
       </c>
       <c r="G144" t="n">
-        <v>0.03225137880245798</v>
+        <v>0.03327928022665536</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.03541654742426935</v>
+        <v>0.03462650420177494</v>
       </c>
       <c r="B145" t="n">
-        <v>0.02823872042164119</v>
+        <v>0.02808221639286968</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1381541493720908</v>
+        <v>0.1379094466020811</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3360564330819585</v>
+        <v>0.3344742043523785</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3707881566615391</v>
+        <v>0.3727150412943429</v>
       </c>
       <c r="F145" t="n">
-        <v>0.05905870087630537</v>
+        <v>0.05887405978337498</v>
       </c>
       <c r="G145" t="n">
-        <v>0.03228729216219584</v>
+        <v>0.03331852737317847</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.03547782355765461</v>
+        <v>0.03467533488031627</v>
       </c>
       <c r="B146" t="n">
-        <v>0.02824567030055964</v>
+        <v>0.02809278300902191</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1382229051515125</v>
+        <v>0.1379819926131514</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3371500649774691</v>
+        <v>0.3352510083867408</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3695086894732121</v>
+        <v>0.3717466123896953</v>
       </c>
       <c r="F146" t="n">
-        <v>0.05907271909312641</v>
+        <v>0.0588960314822427</v>
       </c>
       <c r="G146" t="n">
-        <v>0.03232212744646601</v>
+        <v>0.03335623723883158</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.03553849598201078</v>
+        <v>0.03472377487284375</v>
       </c>
       <c r="B147" t="n">
-        <v>0.02825246884046387</v>
+        <v>0.0281035304116125</v>
       </c>
       <c r="C147" t="n">
-        <v>0.138291933817069</v>
+        <v>0.1380562859797186</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3381909324214903</v>
+        <v>0.3359647459677693</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3682869269362793</v>
+        <v>0.3708451525920428</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0590831997752502</v>
+        <v>0.05891390160482324</v>
       </c>
       <c r="G147" t="n">
-        <v>0.03235604222743645</v>
+        <v>0.03339260857118957</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.03559819181308074</v>
+        <v>0.03477145575135401</v>
       </c>
       <c r="B148" t="n">
-        <v>0.02825921537636034</v>
+        <v>0.02811449650536529</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1383608906749244</v>
+        <v>0.1381318098439374</v>
       </c>
       <c r="D148" t="n">
-        <v>0.339161683714519</v>
+        <v>0.3366056270425347</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3671400921903827</v>
+        <v>0.3700204509161842</v>
       </c>
       <c r="F148" t="n">
-        <v>0.05909072061580542</v>
+        <v>0.05892830320071063</v>
       </c>
       <c r="G148" t="n">
-        <v>0.03238920561492753</v>
+        <v>0.03342785673991366</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.03565656058037749</v>
+        <v>0.03481803311734277</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0282660088682235</v>
+        <v>0.02812571465129275</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1384294134911647</v>
+        <v>0.1382080028209438</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3400472041850186</v>
+        <v>0.3371659318292516</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3660832030051189</v>
+        <v>0.3692802581101263</v>
       </c>
       <c r="F149" t="n">
-        <v>0.05909581889849818</v>
+        <v>0.05893985408142501</v>
       </c>
       <c r="G149" t="n">
-        <v>0.03242179097159829</v>
+        <v>0.03346220538961735</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.03571328086743918</v>
+        <v>0.03486319364470559</v>
       </c>
       <c r="B150" t="n">
-        <v>0.02827294640947571</v>
+        <v>0.02813721511584645</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1384971388031354</v>
+        <v>0.138284278177931</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3408349182044979</v>
+        <v>0.3376401389436117</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3651287631656919</v>
+        <v>0.3686301535505173</v>
       </c>
       <c r="F150" t="n">
-        <v>0.05909898409956848</v>
+        <v>0.05894914286159366</v>
       </c>
       <c r="G150" t="n">
-        <v>0.03245396845019126</v>
+        <v>0.03349587770579483</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.0357680653966728</v>
+        <v>0.03490666051116498</v>
       </c>
       <c r="B151" t="n">
-        <v>0.02828012164798241</v>
+        <v>0.02814902638804952</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1385637161894264</v>
+        <v>0.1383600416770146</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3415149729766711</v>
+        <v>0.3380249471133722</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3642865729015716</v>
+        <v>0.3680735196464557</v>
       </c>
       <c r="F151" t="n">
-        <v>0.05910065310896079</v>
+        <v>0.05895671687929771</v>
       </c>
       <c r="G151" t="n">
-        <v>0.03248589777871498</v>
+        <v>0.03352908778464547</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.03582066457391686</v>
+        <v>0.03494819719770425</v>
       </c>
       <c r="B152" t="n">
-        <v>0.02828762309474944</v>
+        <v>0.02816117613745746</v>
       </c>
       <c r="C152" t="n">
-        <v>0.138628820010785</v>
+        <v>0.1384347076113438</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3420803067298461</v>
+        <v>0.3383191991987965</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3635636559443381</v>
+        <v>0.3676116149155589</v>
       </c>
       <c r="F152" t="n">
-        <v>0.05910120793499316</v>
+        <v>0.05896307234311458</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0325177217113715</v>
+        <v>0.03356203259602468</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.03587086857123077</v>
+        <v>0.03498760970496913</v>
       </c>
       <c r="B153" t="n">
-        <v>0.02829553231801982</v>
+        <v>0.02817369164492738</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1386921583386829</v>
+        <v>0.1385077127264086</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3425266094060732</v>
+        <v>0.3385237217738669</v>
       </c>
       <c r="E153" t="n">
-        <v>0.3629642951862651</v>
+        <v>0.3672437322415593</v>
       </c>
       <c r="F153" t="n">
-        <v>0.05910097565198828</v>
+        <v>0.05896864691445688</v>
       </c>
       <c r="G153" t="n">
-        <v>0.03254956052773975</v>
+        <v>0.03359488499381186</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.03591850807351359</v>
+        <v>0.03502474729503149</v>
       </c>
       <c r="B154" t="n">
-        <v>0.02830392205175937</v>
+        <v>0.02818659961422031</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1387534789128942</v>
+        <v>0.1385785278757087</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3428521887149455</v>
+        <v>0.3386410967809063</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3624901640849004</v>
+        <v>0.3669674254762254</v>
       </c>
       <c r="F154" t="n">
-        <v>0.05910023026228636</v>
+        <v>0.05897381479640976</v>
       </c>
       <c r="G154" t="n">
-        <v>0.03258150789970087</v>
+        <v>0.03362778816149804</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.03596345385275024</v>
+        <v>0.0350595019141158</v>
       </c>
       <c r="B155" t="n">
-        <v>0.02831285427442096</v>
+        <v>0.02819992535311014</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1388125722181565</v>
+        <v>0.1386466674000935</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3430577580371375</v>
+        <v>0.3386753837385374</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3621405371821796</v>
+        <v>0.3667787855304723</v>
       </c>
       <c r="F155" t="n">
-        <v>0.05909919607864503</v>
+        <v>0.05897888427752125</v>
       </c>
       <c r="G155" t="n">
-        <v>0.03261362835671024</v>
+        <v>0.03366085178614943</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.03600561535895531</v>
+        <v>0.03509180648604526</v>
       </c>
       <c r="B156" t="n">
-        <v>0.02832237833667911</v>
+        <v>0.02821369138744812</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1388692719246616</v>
+        <v>0.1387116963305263</v>
       </c>
       <c r="D156" t="n">
-        <v>0.3431461650549635</v>
+        <v>0.3386318117002217</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3619125606460543</v>
+        <v>0.3666727463784773</v>
       </c>
       <c r="F156" t="n">
-        <v>0.05909805220635218</v>
+        <v>0.05898409757910555</v>
       </c>
       <c r="G156" t="n">
-        <v>0.03264595647233367</v>
+        <v>0.03369415013817591</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.03604493852729569</v>
+        <v>0.03512163228684231</v>
       </c>
       <c r="B157" t="n">
-        <v>0.02833252923069117</v>
+        <v>0.02822791563220198</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1389234530888409</v>
+        <v>0.138773235589498</v>
       </c>
       <c r="D157" t="n">
-        <v>0.3431220810367425</v>
+        <v>0.3385164597144882</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3618015626266255</v>
+        <v>0.3666434018903135</v>
       </c>
       <c r="F157" t="n">
-        <v>0.05909693771416231</v>
+        <v>0.05898963278053802</v>
       </c>
       <c r="G157" t="n">
-        <v>0.03267849777564235</v>
+        <v>0.03372772210611828</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.0360814030033514</v>
+        <v>0.03514898561911858</v>
       </c>
       <c r="B158" t="n">
-        <v>0.02834332609682353</v>
+        <v>0.02824260928472032</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1389750286397768</v>
+        <v>0.1388309654080491</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3429916703391178</v>
+        <v>0.3383359430603463</v>
       </c>
       <c r="E158" t="n">
-        <v>0.361801383530526</v>
+        <v>0.3666843159754728</v>
       </c>
       <c r="F158" t="n">
-        <v>0.05909595711978917</v>
+        <v>0.05899560754722168</v>
       </c>
       <c r="G158" t="n">
-        <v>0.03271123127061538</v>
+        <v>0.03376157310507107</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.03611501897473169</v>
+        <v>0.03517390400139042</v>
       </c>
       <c r="B159" t="n">
-        <v>0.02835477106175733</v>
+        <v>0.02825777462601315</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1390239446801954</v>
+        <v>0.13888462718776</v>
       </c>
       <c r="D159" t="n">
-        <v>0.3427622582216948</v>
+        <v>0.3380971202209125</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3619047078521107</v>
+        <v>0.366788810952808</v>
       </c>
       <c r="F159" t="n">
-        <v>0.05909518587390408</v>
+        <v>0.05900208435625032</v>
       </c>
       <c r="G159" t="n">
-        <v>0.03274411333560607</v>
+        <v>0.03379567865486555</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>0.03614582378185212</v>
+        <v>0.03519645207450749</v>
       </c>
       <c r="B160" t="n">
-        <v>0.02836684848595841</v>
+        <v>0.02827340291722435</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1390701752035427</v>
+        <v>0.1389340240324321</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3424420124802038</v>
+        <v>0.3378068326570503</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3621033817665315</v>
+        <v>0.3669502220983343</v>
       </c>
       <c r="F160" t="n">
-        <v>0.05909467559917671</v>
+        <v>0.05900907690063149</v>
       </c>
       <c r="G160" t="n">
-        <v>0.03277708268273469</v>
+        <v>0.03382998931982005</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0.03617387845354954</v>
+        <v>0.03521671740670954</v>
       </c>
       <c r="B161" t="n">
-        <v>0.02837952468416877</v>
+        <v>0.02828947256425374</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1391137167417214</v>
+        <v>0.1389790201605021</v>
       </c>
       <c r="D161" t="n">
-        <v>0.3420396513601872</v>
+        <v>0.3374716862277002</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3623887038605636</v>
+        <v>0.3671621096676393</v>
       </c>
       <c r="F161" t="n">
-        <v>0.05909445890656816</v>
+        <v>0.05901655734920588</v>
       </c>
       <c r="G161" t="n">
-        <v>0.03281006599324143</v>
+        <v>0.03386443662398948</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0.03619926428539014</v>
+        <v>0.0352348063530181</v>
       </c>
       <c r="B162" t="n">
-        <v>0.02839274816434119</v>
+        <v>0.02830594769884843</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1391545833735136</v>
+        <v>0.1390195393946842</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3415641868006609</v>
+        <v>0.3370978798430039</v>
       </c>
       <c r="E162" t="n">
-        <v>0.3627516798944997</v>
+        <v>0.3674184230580028</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0590945536673313</v>
+        <v>0.05902446414203159</v>
       </c>
       <c r="G162" t="n">
-        <v>0.03284298381426352</v>
+        <v>0.03389893951041072</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0.03622207955410653</v>
+        <v>0.03525084009586518</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0284064504036436</v>
+        <v>0.02832277729356219</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1391928024944324</v>
+        <v>0.1390555629153081</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3410247086309262</v>
+        <v>0.3366910838521991</v>
       </c>
       <c r="E163" t="n">
-        <v>0.363183235933983</v>
+        <v>0.3677136149328907</v>
       </c>
       <c r="F163" t="n">
-        <v>0.05909496667736223</v>
+        <v>0.05903271000799921</v>
       </c>
       <c r="G163" t="n">
-        <v>0.03287575630554623</v>
+        <v>0.03393341090217542</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0.03624243643068351</v>
+        <v>0.03526495096452224</v>
       </c>
       <c r="B164" t="n">
-        <v>0.02842054716410086</v>
+        <v>0.0283398948950364</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1392284115789148</v>
+        <v>0.1390871264575755</v>
       </c>
       <c r="D164" t="n">
-        <v>0.3404302123126977</v>
+        <v>0.3362563679214022</v>
       </c>
       <c r="E164" t="n">
-        <v>0.3636743873769153</v>
+        <v>0.36804270591243</v>
       </c>
       <c r="F164" t="n">
-        <v>0.05909569667605932</v>
+        <v>0.0590411899021212</v>
       </c>
       <c r="G164" t="n">
-        <v>0.03290830846062872</v>
+        <v>0.03396776394691209</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>0.03626045813503758</v>
+        <v>0.03527727910250839</v>
       </c>
       <c r="B165" t="n">
-        <v>0.02843494032703499</v>
+        <v>0.02835721902663417</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1392614560942009</v>
+        <v>0.1391143171297834</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3397894700607267</v>
+        <v>0.3357981758254949</v>
       </c>
       <c r="E165" t="n">
-        <v>0.364216364177209</v>
+        <v>0.3684013027612085</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05909673671483581</v>
+        <v>0.05904978857511112</v>
       </c>
       <c r="G165" t="n">
-        <v>0.03294057449095463</v>
+        <v>0.03400191757925962</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>0.03627627635469154</v>
+        <v>0.03528796952641074</v>
       </c>
       <c r="B166" t="n">
-        <v>0.02844952020580844</v>
+        <v>0.02837465427873796</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1392919886140154</v>
+        <v>0.1391372700261267</v>
       </c>
       <c r="D166" t="n">
-        <v>0.33911094294724</v>
+        <v>0.3353203426842</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3648006948464415</v>
+        <v>0.3687855748613161</v>
       </c>
       <c r="F166" t="n">
-        <v>0.05909807588776174</v>
+        <v>0.05905838751095892</v>
       </c>
       <c r="G166" t="n">
-        <v>0.03297250114404159</v>
+        <v>0.03403580111224945</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>0.03629002893484421</v>
+        <v>0.03529716959666037</v>
       </c>
       <c r="B167" t="n">
-        <v>0.02846416827683964</v>
+        <v>0.0283920930722803</v>
       </c>
       <c r="C167" t="n">
-        <v>0.1393200690964374</v>
+        <v>0.1391561647987677</v>
       </c>
       <c r="D167" t="n">
-        <v>0.3384027298230124</v>
+        <v>0.3348261486942619</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3654192535950249</v>
+        <v>0.3691921951782808</v>
       </c>
       <c r="F167" t="n">
-        <v>0.05909970045389034</v>
+        <v>0.05906687100101411</v>
       </c>
       <c r="G167" t="n">
-        <v>0.03300404981995111</v>
+        <v>0.034069357658735</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0.03630185783797572</v>
+        <v>0.03530502690126249</v>
       </c>
       <c r="B168" t="n">
-        <v>0.02847876024808144</v>
+        <v>0.02840941804796163</v>
       </c>
       <c r="C168" t="n">
-        <v>0.1393457662269224</v>
+        <v>0.1391712223363067</v>
       </c>
       <c r="D168" t="n">
-        <v>0.3376725475934855</v>
+        <v>0.3343184023085717</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3660642762416502</v>
+        <v>0.3696182529575663</v>
       </c>
       <c r="F168" t="n">
-        <v>0.05910159440554884</v>
+        <v>0.05907513116858978</v>
       </c>
       <c r="G168" t="n">
-        <v>0.03303519744633622</v>
+        <v>0.03410254627974113</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0.03631190736118724</v>
+        <v>0.03531168753666239</v>
       </c>
       <c r="B169" t="n">
-        <v>0.02849316936803239</v>
+        <v>0.02842650500009572</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1393691596447789</v>
+        <v>0.1391827016647892</v>
       </c>
       <c r="D169" t="n">
-        <v>0.3369277365335306</v>
+        <v>0.3337995450585254</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3667283513811738</v>
+        <v>0.3700611460744312</v>
       </c>
       <c r="F169" t="n">
-        <v>0.05910373955114944</v>
+        <v>0.05908307181614746</v>
       </c>
       <c r="G169" t="n">
-        <v>0.03306593616014736</v>
+        <v>0.03413534284934869</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.03632032259590402</v>
+        <v>0.03531729475580283</v>
       </c>
       <c r="B170" t="n">
-        <v>0.02850726986054799</v>
+        <v>0.02844322624111706</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1393903428338189</v>
+        <v>0.1391908971411086</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3361752838716925</v>
+        <v>0.3332717697845314</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3674043937050248</v>
+        <v>0.370518461332752</v>
       </c>
       <c r="F170" t="n">
-        <v>0.05910611521163241</v>
+        <v>0.0590906110361336</v>
       </c>
       <c r="G170" t="n">
-        <v>0.03309627192137941</v>
+        <v>0.03416773970855441</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.03632724811174612</v>
+        <v>0.03532198794126085</v>
       </c>
       <c r="B171" t="n">
-        <v>0.02852094035680649</v>
+        <v>0.02845945425303699</v>
       </c>
       <c r="C171" t="n">
-        <v>0.1394094264148503</v>
+        <v>0.1391961359454051</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3354218588028923</v>
+        <v>0.3327371439249504</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3680856064183044</v>
+        <v>0.3709878510851898</v>
       </c>
       <c r="F171" t="n">
-        <v>0.05910869765242868</v>
+        <v>0.0590976826014547</v>
       </c>
       <c r="G171" t="n">
-        <v>0.03312622224297136</v>
+        <v>0.03419974424870209</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0.03633282684163407</v>
+        <v>0.03532590185128611</v>
       </c>
       <c r="B172" t="n">
-        <v>0.02853406719138086</v>
+        <v>0.02847506545834778</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1394265415312068</v>
+        <v>0.1391987758024966</v>
       </c>
       <c r="D172" t="n">
-        <v>0.3346738522979839</v>
+        <v>0.3321977297141442</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3687654394899142</v>
+        <v>0.3714669143318369</v>
       </c>
       <c r="F172" t="n">
-        <v>0.05911145938621751</v>
+        <v>0.05910423622605263</v>
       </c>
       <c r="G172" t="n">
-        <v>0.03315581326166251</v>
+        <v>0.03423137661583584</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0.03633719914431455</v>
+        <v>0.03532916607868338</v>
       </c>
       <c r="B173" t="n">
-        <v>0.02854654742744302</v>
+        <v>0.02848994392869563</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1394418429963042</v>
+        <v>0.1391992027778297</v>
       </c>
       <c r="D173" t="n">
-        <v>0.3339374155468191</v>
+        <v>0.3316556936537424</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3694375499959102</v>
+        <v>0.3719530899484865</v>
       </c>
       <c r="F173" t="n">
-        <v>0.05911436849313333</v>
+        <v>0.05911023685285886</v>
       </c>
       <c r="G173" t="n">
-        <v>0.03318507639607533</v>
+        <v>0.03426266675970353</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0.03634050201706302</v>
+        <v>0.03533190465766228</v>
       </c>
       <c r="B174" t="n">
-        <v>0.02855829148721708</v>
+        <v>0.02850398484797984</v>
       </c>
       <c r="C174" t="n">
-        <v>0.139455511847293</v>
+        <v>0.1391978289120606</v>
       </c>
       <c r="D174" t="n">
-        <v>0.3332184915610798</v>
+        <v>0.3311133984442471</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3700957701462313</v>
+        <v>0.3724435688929176</v>
       </c>
       <c r="F174" t="n">
-        <v>0.05911738809914237</v>
+        <v>0.05911566317865806</v>
       </c>
       <c r="G174" t="n">
-        <v>0.03321404484197362</v>
+        <v>0.03429365106647451</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0.03634286842928922</v>
+        <v>0.03533423575230658</v>
       </c>
       <c r="B175" t="n">
-        <v>0.02856922528049621</v>
+        <v>0.02851709755823978</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1394677569726644</v>
+        <v>0.1391950893904082</v>
       </c>
       <c r="D175" t="n">
-        <v>0.3325228353969218</v>
+        <v>0.3305734716891475</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3707340876477144</v>
+        <v>0.3729352311385595</v>
       </c>
       <c r="F175" t="n">
-        <v>0.05912047613128624</v>
+        <v>0.05912050565743088</v>
       </c>
       <c r="G175" t="n">
-        <v>0.03324275014162771</v>
+        <v>0.03432436881390722</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.0363444267457396</v>
+        <v>0.03533627136353386</v>
       </c>
       <c r="B176" t="n">
-        <v>0.02857929175375815</v>
+        <v>0.02852920804212851</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1394788154713517</v>
+        <v>0.1391914389050951</v>
       </c>
       <c r="D176" t="n">
-        <v>0.3318560195485422</v>
+        <v>0.3300388470930494</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3713466420005162</v>
+        <v>0.3734246116878445</v>
       </c>
       <c r="F176" t="n">
-        <v>0.05912358543917157</v>
+        <v>0.05912476423375749</v>
       </c>
       <c r="G176" t="n">
-        <v>0.03327121904092085</v>
+        <v>0.03435485867459087</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.03634530020844945</v>
+        <v>0.03533811699964603</v>
       </c>
       <c r="B177" t="n">
-        <v>0.02858845181369011</v>
+        <v>0.02854026073215281</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1394889514812941</v>
+        <v>0.1391873468715515</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3312234224481508</v>
+        <v>0.3295127755480205</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3719277389074941</v>
+        <v>0.3739078983339674</v>
       </c>
       <c r="F177" t="n">
-        <v>0.05912666432899184</v>
+        <v>0.05912844604524171</v>
       </c>
       <c r="G177" t="n">
-        <v>0.03329947081192946</v>
+        <v>0.03438515546942014</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.03634560644662805</v>
+        <v>0.03533987126899765</v>
       </c>
       <c r="B178" t="n">
-        <v>0.02859668461624211</v>
+        <v>0.02855021958095398</v>
       </c>
       <c r="C178" t="n">
-        <v>0.1394984532790656</v>
+        <v>0.139183291210543</v>
       </c>
       <c r="D178" t="n">
-        <v>0.3306301995306987</v>
+        <v>0.3289988053868804</v>
       </c>
       <c r="E178" t="n">
-        <v>0.3724718834410826</v>
+        <v>0.3743809619092228</v>
       </c>
       <c r="F178" t="n">
-        <v>0.05912965750973778</v>
+        <v>0.05913156330124283</v>
       </c>
       <c r="G178" t="n">
-        <v>0.03332751517654523</v>
+        <v>0.03441528734215939</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.03634545698973846</v>
+        <v>0.03534162537158037</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0286039872478794</v>
+        <v>0.02855906837409721</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1395076285683196</v>
+        <v>0.1391797505140879</v>
       </c>
       <c r="D179" t="n">
-        <v>0.3300812379869862</v>
+        <v>0.3285007331023262</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3729738308760972</v>
+        <v>0.3748394176499461</v>
       </c>
       <c r="F179" t="n">
-        <v>0.05913250740904465</v>
+        <v>0.05913413149880918</v>
       </c>
       <c r="G179" t="n">
-        <v>0.03335535092193433</v>
+        <v>0.03444527348915288</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.03634495676705656</v>
+        <v>0.03534346248776718</v>
       </c>
       <c r="B180" t="n">
-        <v>0.02861037385502463</v>
+        <v>0.02856681031240516</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1395167979993919</v>
+        <v>0.1391771945640633</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3295810979883584</v>
+        <v>0.3280225278614816</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3734286523563174</v>
+        <v>0.3752787141547632</v>
       </c>
       <c r="F180" t="n">
-        <v>0.05913515578229415</v>
+        <v>0.0591361680814539</v>
       </c>
       <c r="G180" t="n">
-        <v>0.03338296525155693</v>
+        <v>0.03447512253806576</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.03634420358339595</v>
+        <v>0.03534545708546628</v>
       </c>
       <c r="B181" t="n">
-        <v>0.02861587430339583</v>
+        <v>0.02857346693095603</v>
       </c>
       <c r="C181" t="n">
-        <v>0.1395262871106751</v>
+        <v>0.1391760733607478</v>
       </c>
       <c r="D181" t="n">
-        <v>0.3291339446123512</v>
+        <v>0.3275682350221119</v>
       </c>
       <c r="E181" t="n">
-        <v>0.3738318110152775</v>
+        <v>0.3756942443838207</v>
       </c>
       <c r="F181" t="n">
-        <v>0.05913754550582818</v>
+        <v>0.05913769158870502</v>
       </c>
       <c r="G181" t="n">
-        <v>0.03341033386907628</v>
+        <v>0.03450483162819217</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.03634328757640496</v>
+        <v>0.03534767418840462</v>
       </c>
       <c r="B182" t="n">
-        <v>0.02862053245963484</v>
+        <v>0.02857907645344044</v>
       </c>
       <c r="C182" t="n">
-        <v>0.1395364170139202</v>
+        <v>0.1391768050213707</v>
       </c>
       <c r="D182" t="n">
-        <v>0.3287434758209385</v>
+        <v>0.3271418653899379</v>
       </c>
       <c r="E182" t="n">
-        <v>0.3741792429342305</v>
+        <v>0.3760814714538714</v>
       </c>
       <c r="F182" t="n">
-        <v>0.05913962244218983</v>
+        <v>0.05913872128866059</v>
       </c>
       <c r="G182" t="n">
-        <v>0.03343742175268102</v>
+        <v>0.03453438620431409</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.03634229066925086</v>
+        <v>0.03535016866558829</v>
       </c>
       <c r="B183" t="n">
-        <v>0.02862440419662601</v>
+        <v>0.02858369170178892</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1395474942735317</v>
+        <v>0.1391797631029475</v>
       </c>
       <c r="D183" t="n">
-        <v>0.328412852397057</v>
+        <v>0.326747277956229</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3744674366645349</v>
+        <v>0.3764360608375278</v>
       </c>
       <c r="F183" t="n">
-        <v>0.05914133725683141</v>
+        <v>0.05913927723738253</v>
       </c>
       <c r="G183" t="n">
-        <v>0.03346418454216834</v>
+        <v>0.03456376049853629</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0.03634128604522947</v>
+        <v>0.0353529846126341</v>
       </c>
       <c r="B184" t="n">
-        <v>0.02862755521564813</v>
+        <v>0.02858737769166987</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1395598005541558</v>
+        <v>0.1391852640647704</v>
       </c>
       <c r="D184" t="n">
-        <v>0.3281446356506247</v>
+        <v>0.3263880641776471</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3746935050228356</v>
+        <v>0.3767540101415509</v>
       </c>
       <c r="F184" t="n">
-        <v>0.05914264707912137</v>
+        <v>0.05913938067020521</v>
       </c>
       <c r="G184" t="n">
-        <v>0.03349057043238474</v>
+        <v>0.03459291864152215</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.03634033767988262</v>
+        <v>0.03535615489759872</v>
       </c>
       <c r="B185" t="n">
-        <v>0.02863005877461907</v>
+        <v>0.02859020904501367</v>
       </c>
       <c r="C185" t="n">
-        <v>0.139573582635506</v>
+        <v>0.1391935556876364</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3279407379597312</v>
+        <v>0.3260674414369512</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3748552435788854</v>
+        <v>0.3770317680118334</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0591435169203135</v>
+        <v>0.0591390546036915</v>
       </c>
       <c r="G185" t="n">
-        <v>0.03351652245106212</v>
+        <v>0.03462181631727532</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.03633949996830599</v>
+        <v>0.03535970093700056</v>
       </c>
       <c r="B186" t="n">
-        <v>0.02863199339709534</v>
+        <v>0.02859226734319236</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1395890434271845</v>
+        <v>0.1392048072954176</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3278023898427643</v>
+        <v>0.3257881621873326</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3749511716019695</v>
+        <v>0.3772663348676258</v>
       </c>
       <c r="F186" t="n">
-        <v>0.05914392077775516</v>
+        <v>0.0591383245142653</v>
       </c>
       <c r="G186" t="n">
-        <v>0.03354198098492552</v>
+        <v>0.03465040285516588</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.03633881748858393</v>
+        <v>0.03536363275222237</v>
       </c>
       <c r="B187" t="n">
-        <v>0.02863344062476114</v>
+        <v>0.02859363853038884</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1396063345739459</v>
+        <v>0.1392191025677335</v>
       </c>
       <c r="D187" t="n">
-        <v>0.3277301255507324</v>
+        <v>0.3255524435731453</v>
       </c>
       <c r="E187" t="n">
-        <v>0.3749805529625844</v>
+        <v>0.3774553399775687</v>
       </c>
       <c r="F187" t="n">
-        <v>0.05914384238195064</v>
+        <v>0.05913721896029343</v>
       </c>
       <c r="G187" t="n">
-        <v>0.03356688641744153</v>
+        <v>0.03467862363864775</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.03633832493583097</v>
+        <v>0.0353679493348919</v>
       </c>
       <c r="B188" t="n">
-        <v>0.02863448286749931</v>
+        <v>0.02859441045899273</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1396255511360067</v>
+        <v>0.1392364355920183</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3277237872880073</v>
+        <v>0.3253619202618107</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3749433964645913</v>
+        <v>0.3775970916218779</v>
       </c>
       <c r="F188" t="n">
-        <v>0.0591432755633738</v>
+        <v>0.05913577002823305</v>
       </c>
       <c r="G188" t="n">
-        <v>0.03359118174469058</v>
+        <v>0.03470642270217558</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0.0363380472540048</v>
+        <v>0.03537263932467664</v>
       </c>
       <c r="B189" t="n">
-        <v>0.02863520139628082</v>
+        <v>0.02859467064906466</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1396467287015684</v>
+        <v>0.1392567105907762</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3277825464415392</v>
+        <v>0.3252176210829443</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3748404369245512</v>
+        <v>0.3776905994588536</v>
       </c>
       <c r="F189" t="n">
-        <v>0.05914222423659088</v>
+        <v>0.05913401350852298</v>
       </c>
       <c r="G189" t="n">
-        <v>0.03361481504546431</v>
+        <v>0.03473374538516169</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0.03633799997934747</v>
+        <v>0.03537768197777474</v>
       </c>
       <c r="B190" t="n">
-        <v>0.02863567452057647</v>
+        <v>0.02859450431453016</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1396698430905632</v>
+        <v>0.1392797454935852</v>
       </c>
       <c r="D190" t="n">
-        <v>0.3279049388538556</v>
+        <v>0.3251199681209119</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3746730998421174</v>
+        <v>0.3777355704396458</v>
       </c>
       <c r="F190" t="n">
-        <v>0.05914070201825863</v>
+        <v>0.05913198873990974</v>
       </c>
       <c r="G190" t="n">
-        <v>0.03363774169528144</v>
+        <v>0.03476054091364287</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0.03633818979536763</v>
+        <v>0.03538304838190069</v>
       </c>
       <c r="B191" t="n">
-        <v>0.02863597598661126</v>
+        <v>0.02859399269049592</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1396948126197962</v>
+        <v>0.1393052792310051</v>
       </c>
       <c r="D191" t="n">
-        <v>0.3280889103400975</v>
+        <v>0.3250687953621166</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3744434535193494</v>
+        <v>0.3777323814487754</v>
       </c>
       <c r="F191" t="n">
-        <v>0.05913873150879136</v>
+        <v>0.05912973809928448</v>
       </c>
       <c r="G191" t="n">
-        <v>0.03365992622998622</v>
+        <v>0.03478676478642189</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0.03633861528645388</v>
+        <v>0.03538870285636949</v>
       </c>
       <c r="B192" t="n">
-        <v>0.02863617362860245</v>
+        <v>0.02859321168032519</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1397215027266775</v>
+        <v>0.1393329823395092</v>
       </c>
       <c r="D192" t="n">
-        <v>0.3283318684447202</v>
+        <v>0.3250633829967094</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3741541528427749</v>
+        <v>0.3776820331217846</v>
       </c>
       <c r="F192" t="n">
-        <v>0.05913634328631465</v>
+        <v>0.05912730615314511</v>
       </c>
       <c r="G192" t="n">
-        <v>0.03368134378445648</v>
+        <v>0.03481238085215694</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.03633926786011604</v>
+        <v>0.03539460446509884</v>
       </c>
       <c r="B193" t="n">
-        <v>0.02863632830334433</v>
+        <v>0.02859223082765117</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1397497325033511</v>
+        <v>0.1393624702130816</v>
       </c>
       <c r="D193" t="n">
-        <v>0.3286307367549783</v>
+        <v>0.3251025030549162</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3738083788552856</v>
+        <v>0.3775860899379699</v>
       </c>
       <c r="F193" t="n">
-        <v>0.05913357467030108</v>
+        <v>0.05912473852362888</v>
       </c>
       <c r="G193" t="n">
-        <v>0.03370198105262366</v>
+        <v>0.03483736297765338</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.03634013279960823</v>
+        <v>0.03540070856652106</v>
       </c>
       <c r="B194" t="n">
-        <v>0.02863649312590367</v>
+        <v>0.02859111260750078</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1397792826295247</v>
+        <v>0.1393933181469795</v>
       </c>
       <c r="D194" t="n">
-        <v>0.3289820088595175</v>
+        <v>0.3251844721748424</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3734097775236696</v>
+        <v>0.3774466117260019</v>
       </c>
       <c r="F194" t="n">
-        <v>0.05913046832582149</v>
+        <v>0.05912208055271944</v>
       </c>
       <c r="G194" t="n">
-        <v>0.03372183673595475</v>
+        <v>0.03486169622543488</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.03634119039917335</v>
+        <v>0.03540696832676776</v>
       </c>
       <c r="B195" t="n">
-        <v>0.02863671301642092</v>
+        <v>0.02858991202169246</v>
       </c>
       <c r="C195" t="n">
-        <v>0.139809904073238</v>
+        <v>0.1394250772106251</v>
       </c>
       <c r="D195" t="n">
-        <v>0.3293818000809933</v>
+        <v>0.3253072078373614</v>
       </c>
       <c r="E195" t="n">
-        <v>0.372962400173683</v>
+        <v>0.3772660812528152</v>
       </c>
       <c r="F195" t="n">
-        <v>0.05912707078573397</v>
+        <v>0.05911937587022086</v>
       </c>
       <c r="G195" t="n">
-        <v>0.03374092147075758</v>
+        <v>0.03488537748051712</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.03634241713102467</v>
+        <v>0.03541333613041456</v>
       </c>
       <c r="B196" t="n">
-        <v>0.02863702455569586</v>
+        <v>0.02858867647622952</v>
       </c>
       <c r="C196" t="n">
-        <v>0.13984132692878</v>
+        <v>0.1394572899730388</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3298258962463466</v>
+        <v>0.3254682852121913</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3724706469174559</v>
+        <v>0.3770473317329692</v>
       </c>
       <c r="F196" t="n">
-        <v>0.05912343097296106</v>
+        <v>0.0591166649826983</v>
       </c>
       <c r="G196" t="n">
-        <v>0.03375925724773617</v>
+        <v>0.03490841549245841</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0.03634378679226317</v>
+        <v>0.03541976483483902</v>
       </c>
       <c r="B197" t="n">
-        <v>0.02863745613261189</v>
+        <v>0.02858744591210861</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1398732688252415</v>
+        <v>0.1394895051832672</v>
       </c>
       <c r="D197" t="n">
-        <v>0.3303097997993236</v>
+        <v>0.325664992684809</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3719392132928046</v>
+        <v>0.3767934770567508</v>
       </c>
       <c r="F197" t="n">
-        <v>0.05911959880000539</v>
+        <v>0.05911398400034575</v>
       </c>
       <c r="G197" t="n">
-        <v>0.03377687635775005</v>
+        <v>0.03493083032787954</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.0363452715855791</v>
+        <v>0.03542620882889769</v>
       </c>
       <c r="B198" t="n">
-        <v>0.02863802835541874</v>
+        <v>0.02858625315571778</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1399054424449185</v>
+        <v>0.1395212906703309</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3308287743891768</v>
+        <v>0.3258943850303586</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3713730393879915</v>
+        <v>0.376507846447282</v>
       </c>
       <c r="F198" t="n">
-        <v>0.05911562391628294</v>
+        <v>0.05911136360741694</v>
       </c>
       <c r="G198" t="n">
-        <v>0.03379381992063219</v>
+        <v>0.03495265225999625</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0.03634684309497551</v>
+        <v>0.03543262487234308</v>
       </c>
       <c r="B199" t="n">
-        <v>0.02863875468668166</v>
+        <v>0.02858512445045417</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1399375618941895</v>
+        <v>0.1395522439483256</v>
       </c>
       <c r="D199" t="n">
-        <v>0.3313778895734078</v>
+        <v>0.3261533339705681</v>
       </c>
       <c r="E199" t="n">
-        <v>0.3707772600242016</v>
+        <v>0.3761939242456169</v>
       </c>
       <c r="F199" t="n">
-        <v>0.05911155465620106</v>
+        <v>0.05910882835969335</v>
       </c>
       <c r="G199" t="n">
-        <v>0.03381013607034295</v>
+        <v>0.03497392015299904</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.03634847312630528</v>
+        <v>0.03543897270861603</v>
       </c>
       <c r="B200" t="n">
-        <v>0.02863964225614682</v>
+        <v>0.02858408012778283</v>
       </c>
       <c r="C200" t="n">
-        <v>0.1399693477985618</v>
+        <v>0.1395820002674074</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3319520674158662</v>
+        <v>0.3264385764173669</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3701571542992499</v>
+        <v>0.3758552946875571</v>
       </c>
       <c r="F200" t="n">
-        <v>0.05910743721808019</v>
+        <v>0.0591063963629235</v>
       </c>
       <c r="G200" t="n">
-        <v>0.03382587788578978</v>
+        <v>0.03499467942834612</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0.03635013439604837</v>
+        <v>0.03544521545872085</v>
       </c>
       <c r="B201" t="n">
-        <v>0.02864069280067154</v>
+        <v>0.02858313537333602</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1400005312047599</v>
+        <v>0.1396102381060041</v>
       </c>
       <c r="D201" t="n">
-        <v>0.3325461325504106</v>
+        <v>0.3267467610490206</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3695180927985487</v>
+        <v>0.375495590936939</v>
       </c>
       <c r="F201" t="n">
-        <v>0.05910331508129694</v>
+        <v>0.05910407935122316</v>
       </c>
       <c r="G201" t="n">
-        <v>0.03384110116826372</v>
+        <v>0.03501497972475616</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0.03635180106202986</v>
+        <v>0.03545131981714371</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0286419036784387</v>
+        <v>0.02858230104252456</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1400308565111507</v>
+        <v>0.1396366823248675</v>
       </c>
       <c r="D202" t="n">
-        <v>0.333154866756296</v>
+        <v>0.3270744939785682</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3688654811803368</v>
+        <v>0.3751184473064112</v>
       </c>
       <c r="F202" t="n">
-        <v>0.05909922864053705</v>
+        <v>0.05910188314868624</v>
       </c>
       <c r="G202" t="n">
-        <v>0.03385586217121055</v>
+        <v>0.03503487238179864</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0.03635344910201219</v>
+        <v>0.03545725608140456</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0286432689077827</v>
+        <v>0.0285815844803525</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1400600837303635</v>
+        <v>0.1396611053768299</v>
       </c>
       <c r="D203" t="n">
-        <v>0.3337730683744371</v>
+        <v>0.3274183841812184</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3682046994769312</v>
+        <v>0.3747274535284311</v>
       </c>
       <c r="F203" t="n">
-        <v>0.05909521501727513</v>
+        <v>0.05909980846462876</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0338702153911981</v>
+        <v>0.03505440788713494</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.03635505655527184</v>
+        <v>0.03546299805380172</v>
       </c>
       <c r="B204" t="n">
-        <v>0.02864478018455946</v>
+        <v>0.02858099030201822</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1400879904129867</v>
+        <v>0.1396833270679428</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3343956160779169</v>
+        <v>0.327775089084352</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3675410372518488</v>
+        <v>0.3743261101175259</v>
       </c>
       <c r="F204" t="n">
-        <v>0.05909130799231199</v>
+        <v>0.05909785194573519</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03388421152510462</v>
+        <v>0.03507363342862434</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.03635660364867718</v>
+        <v>0.03546852285723472</v>
       </c>
       <c r="B205" t="n">
-        <v>0.02864642783431379</v>
+        <v>0.02858052109479873</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1401143735503323</v>
+        <v>0.1397032133934776</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3350175356971503</v>
+        <v>0.3281413603309157</v>
       </c>
       <c r="E205" t="n">
-        <v>0.3668796255854469</v>
+        <v>0.3739177842483199</v>
       </c>
       <c r="F205" t="n">
-        <v>0.05908753799591562</v>
+        <v>0.05909600739040072</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03389789568816402</v>
+        <v>0.03509259068485229</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.03635807283409784</v>
+        <v>0.0354738107061145</v>
       </c>
       <c r="B206" t="n">
-        <v>0.02864820166384819</v>
+        <v>0.02858017800752003</v>
       </c>
       <c r="C206" t="n">
-        <v>0.1401390516653018</v>
+        <v>0.1397206749301123</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3356340681530354</v>
+        <v>0.3285140892524499</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3662253676101321</v>
+        <v>0.3735056661101552</v>
       </c>
       <c r="F206" t="n">
-        <v>0.05908393209652917</v>
+        <v>0.05909426702186855</v>
       </c>
       <c r="G206" t="n">
-        <v>0.03391130597705546</v>
+        <v>0.03511131397177937</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.03635944876431439</v>
+        <v>0.03547884466919459</v>
       </c>
       <c r="B207" t="n">
-        <v>0.02865009167979286</v>
+        <v>0.02857996120205612</v>
       </c>
       <c r="C207" t="n">
-        <v>0.1401618672145808</v>
+        <v>0.1397356651669177</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3362407360723888</v>
+        <v>0.3288903510865079</v>
       </c>
       <c r="E207" t="n">
-        <v>0.365582869885105</v>
+        <v>0.3730927263160108</v>
       </c>
       <c r="F207" t="n">
-        <v>0.05908051394078957</v>
+        <v>0.05909262271845492</v>
       </c>
       <c r="G207" t="n">
-        <v>0.03392447244302873</v>
+        <v>0.03512982884085804</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0.03636071823381857</v>
+        <v>0.03548361045368625</v>
       </c>
       <c r="B208" t="n">
-        <v>0.02865208864854033</v>
+        <v>0.02857987015111774</v>
       </c>
       <c r="C208" t="n">
-        <v>0.1401826892929499</v>
+        <v>0.1397481790227817</v>
       </c>
       <c r="D208" t="n">
-        <v>0.3368334064345596</v>
+        <v>0.3292674465041034</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3649563772531764</v>
+        <v>0.3726816755633217</v>
       </c>
       <c r="F208" t="n">
-        <v>0.05907730361594153</v>
+        <v>0.05909106710874076</v>
       </c>
       <c r="G208" t="n">
-        <v>0.03393741652101349</v>
+        <v>0.0351481511962488</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0.03636187010660302</v>
+        <v>0.03548809623105526</v>
       </c>
       <c r="B209" t="n">
-        <v>0.02865418448066648</v>
+        <v>0.02857990377825964</v>
       </c>
       <c r="C209" t="n">
-        <v>0.1402014165070219</v>
+        <v>0.1397582516485794</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3374083466310877</v>
+        <v>0.3296429386432831</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3643497139099579</v>
+        <v>0.3722749282745447</v>
       </c>
       <c r="F209" t="n">
-        <v>0.05907431742591046</v>
+        <v>0.0590895944558286</v>
       </c>
       <c r="G209" t="n">
-        <v>0.03395015093875266</v>
+        <v>0.03516628696844942</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.03636289524863157</v>
+        <v>0.03549229251496699</v>
       </c>
       <c r="B210" t="n">
-        <v>0.02865637242891841</v>
+        <v>0.02858006044830528</v>
       </c>
       <c r="C210" t="n">
-        <v>0.1402179798219185</v>
+        <v>0.1397659574714435</v>
       </c>
       <c r="D210" t="n">
-        <v>0.3379622715385796</v>
+        <v>0.3300146836416544</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3637662332608406</v>
+        <v>0.3718745722985883</v>
       </c>
       <c r="F210" t="n">
-        <v>0.05907156759510655</v>
+        <v>0.05908820127482915</v>
       </c>
       <c r="G210" t="n">
-        <v>0.03396268010600462</v>
+        <v>0.0351842323502122</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0.03636378647654826</v>
+        <v>0.03549619209258141</v>
       </c>
       <c r="B211" t="n">
-        <v>0.0286586470963404</v>
+        <v>0.02858033782881701</v>
       </c>
       <c r="C211" t="n">
-        <v>0.1402323451454998</v>
+        <v>0.1397714093196277</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3384923796067504</v>
+        <v>0.3303808526808107</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3632087787847915</v>
+        <v>0.3714823468594864</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0590690619309099</v>
+        <v>0.05908688664867285</v>
       </c>
       <c r="G211" t="n">
-        <v>0.03397500095916008</v>
+        <v>0.03520197457000381</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>0.03636453852734033</v>
+        <v>0.03549979000271279</v>
       </c>
       <c r="B212" t="n">
-        <v>0.02866100426742292</v>
+        <v>0.02858073265429621</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1402445153527156</v>
+        <v>0.1397747573856932</v>
       </c>
       <c r="D212" t="n">
-        <v>0.3389963765137361</v>
+        <v>0.3307399438301313</v>
       </c>
       <c r="E212" t="n">
-        <v>0.3626796576370863</v>
+        <v>0.3710996307482198</v>
       </c>
       <c r="F212" t="n">
-        <v>0.05906680348555964</v>
+        <v>0.05908565222852239</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0339871042161393</v>
+        <v>0.03521949315042474</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>0.03636514804957748</v>
+        <v>0.03550308354876942</v>
       </c>
       <c r="B213" t="n">
-        <v>0.02866344057902977</v>
+        <v>0.02858124043364843</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1402545315447291</v>
+        <v>0.1397761877438966</v>
       </c>
       <c r="D213" t="n">
-        <v>0.339472485513455</v>
+        <v>0.3310907825068282</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3621806280765976</v>
+        <v>0.3707274422678606</v>
       </c>
       <c r="F213" t="n">
-        <v>0.05906479026436344</v>
+        <v>0.05908450192405105</v>
       </c>
       <c r="G213" t="n">
-        <v>0.03399897597224746</v>
+        <v>0.03523676157494579</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0.03636561361144766</v>
+        <v>0.03550607233153311</v>
       </c>
       <c r="B214" t="n">
-        <v>0.02866595306353651</v>
+        <v>0.02858185514673497</v>
       </c>
       <c r="C214" t="n">
-        <v>0.1402624733298277</v>
+        <v>0.1397759201378166</v>
       </c>
       <c r="D214" t="n">
-        <v>0.3399194442420488</v>
+        <v>0.3314325101043262</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3617129011781437</v>
+        <v>0.370366451706008</v>
       </c>
       <c r="F214" t="n">
-        <v>0.05906301502337663</v>
+        <v>0.0590834413063873</v>
       </c>
       <c r="G214" t="n">
-        <v>0.03401059955161918</v>
+        <v>0.03525374926719382</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0.03636593571882958</v>
+        <v>0.03550875828619634</v>
       </c>
       <c r="B215" t="n">
-        <v>0.02866853860411745</v>
+        <v>0.02858256897708517</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1402684580055017</v>
+        <v>0.1397742047913297</v>
       </c>
       <c r="D215" t="n">
-        <v>0.340336488359439</v>
+        <v>0.3317645611984688</v>
       </c>
       <c r="E215" t="n">
-        <v>0.3612771566074552</v>
+        <v>0.3700170062112393</v>
       </c>
       <c r="F215" t="n">
-        <v>0.05906146519120693</v>
+        <v>0.05908247676214323</v>
       </c>
       <c r="G215" t="n">
-        <v>0.03402195751345018</v>
+        <v>0.03527042377353743</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0.03636611683433859</v>
+        <v>0.0355111457096244</v>
       </c>
       <c r="B216" t="n">
-        <v>0.028671193350424</v>
+        <v>0.02858337212452366</v>
       </c>
       <c r="C216" t="n">
-        <v>0.1402726385714358</v>
+        <v>0.1397713180647274</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3407233229751044</v>
+        <v>0.3320866306075853</v>
       </c>
       <c r="E216" t="n">
-        <v>0.3608735716281298</v>
+        <v>0.3696791660103289</v>
       </c>
       <c r="F216" t="n">
-        <v>0.05906012293742537</v>
+        <v>0.0590816144511154</v>
       </c>
       <c r="G216" t="n">
-        <v>0.03403303370314188</v>
+        <v>0.03528675303209489</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0.03636616138868733</v>
+        <v>0.03551324126662352</v>
       </c>
       <c r="B217" t="n">
-        <v>0.02867391214748784</v>
+        <v>0.02858425273382971</v>
       </c>
       <c r="C217" t="n">
-        <v>0.1402752005741905</v>
+        <v>0.1397675568723807</v>
       </c>
       <c r="D217" t="n">
-        <v>0.3410800833041981</v>
+        <v>0.3323986323380621</v>
       </c>
       <c r="E217" t="n">
-        <v>0.360501861955729</v>
+        <v>0.3693527500465882</v>
       </c>
       <c r="F217" t="n">
-        <v>0.05905896539508838</v>
+        <v>0.05908085913305211</v>
       </c>
       <c r="G217" t="n">
-        <v>0.03404381523461846</v>
+        <v>0.03530270760946343</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0.03636607577704199</v>
+        <v>0.03551505396759951</v>
       </c>
       <c r="B218" t="n">
-        <v>0.02867668803055351</v>
+        <v>0.02858519696445801</v>
       </c>
       <c r="C218" t="n">
-        <v>0.1402763578419491</v>
+        <v>0.1397632318902772</v>
       </c>
       <c r="D218" t="n">
-        <v>0.3414072864011851</v>
+        <v>0.3327006529914663</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3601613326234626</v>
+        <v>0.3690373884561029</v>
       </c>
       <c r="F218" t="n">
-        <v>0.05905796503316339</v>
+        <v>0.05908021293974029</v>
       </c>
       <c r="G218" t="n">
-        <v>0.03405429429264457</v>
+        <v>0.03531826279035589</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0.03636586833371425</v>
+        <v>0.0355165951136329</v>
       </c>
       <c r="B219" t="n">
-        <v>0.02867951183489434</v>
+        <v>0.02858618921279529</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1402763472187322</v>
+        <v>0.1397586597045456</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3417057760855383</v>
+        <v>0.3329929024770356</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3598509367127031</v>
+        <v>0.3687325789008925</v>
       </c>
       <c r="F219" t="n">
-        <v>0.05905709016228727</v>
+        <v>0.0590796741767845</v>
       </c>
       <c r="G219" t="n">
-        <v>0.03406446965213059</v>
+        <v>0.03533340041431369</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0.03636554928130931</v>
+        <v>0.03551787820820897</v>
       </c>
       <c r="B220" t="n">
-        <v>0.0286823719605801</v>
+        <v>0.02858721248404011</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1402754224627069</v>
+        <v>0.1397541541736881</v>
       </c>
       <c r="D220" t="n">
-        <v>0.341976663328001</v>
+        <v>0.3332756648526914</v>
       </c>
       <c r="E220" t="n">
-        <v>0.3595693395907545</v>
+        <v>0.3684377436712781</v>
       </c>
       <c r="F220" t="n">
-        <v>0.05905630555050427</v>
+        <v>0.05907923624284309</v>
       </c>
       <c r="G220" t="n">
-        <v>0.03407434782614389</v>
+        <v>0.03534811036725025</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0.03636513065275279</v>
+        <v>0.03551891883738113</v>
       </c>
       <c r="B221" t="n">
-        <v>0.0286852543199195</v>
+        <v>0.0285882488969237</v>
       </c>
       <c r="C221" t="n">
-        <v>0.1402738475114712</v>
+        <v>0.1397500173876093</v>
       </c>
       <c r="D221" t="n">
-        <v>0.3422212643873247</v>
+        <v>0.3335492518386916</v>
       </c>
       <c r="E221" t="n">
-        <v>0.359314986230626</v>
+        <v>0.3681522846336659</v>
       </c>
       <c r="F221" t="n">
-        <v>0.05905557312309152</v>
+        <v>0.05907888675252457</v>
       </c>
       <c r="G221" t="n">
-        <v>0.03408394377481417</v>
+        <v>0.0353623916532037</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0.03636462618560878</v>
+        <v>0.03551973452174564</v>
       </c>
       <c r="B222" t="n">
-        <v>0.02868814248005858</v>
+        <v>0.02858928029269488</v>
       </c>
       <c r="C222" t="n">
-        <v>0.1402718893611374</v>
+        <v>0.1397465306906014</v>
       </c>
       <c r="D222" t="n">
-        <v>0.3424410388956822</v>
+        <v>0.3338139610841438</v>
       </c>
       <c r="E222" t="n">
-        <v>0.359086169227502</v>
+        <v>0.3678756334780736</v>
       </c>
       <c r="F222" t="n">
-        <v>0.05905485271886517</v>
+        <v>0.05907860694015227</v>
       </c>
       <c r="G222" t="n">
-        <v>0.03409328113114574</v>
+        <v>0.03537625299258872</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0.03636405119003778</v>
+        <v>0.0355203445446103</v>
       </c>
       <c r="B223" t="n">
-        <v>0.02869101799616674</v>
+        <v>0.02859028891111281</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1402698108378019</v>
+        <v>0.1397439462817429</v>
       </c>
       <c r="D223" t="n">
-        <v>0.3426375299092257</v>
+        <v>0.3340700407042261</v>
       </c>
       <c r="E223" t="n">
-        <v>0.3588810952594097</v>
+        <v>0.3676072952349265</v>
       </c>
       <c r="F223" t="n">
-        <v>0.05905410287994561</v>
+        <v>0.05907837140657412</v>
       </c>
       <c r="G223" t="n">
-        <v>0.03410239192741237</v>
+        <v>0.03538971291680754</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0.03636342239297811</v>
+        <v>0.03552076976071268</v>
       </c>
       <c r="B224" t="n">
-        <v>0.02869386091547533</v>
+        <v>0.02859125809093261</v>
       </c>
       <c r="C224" t="n">
-        <v>0.1402678635598401</v>
+        <v>0.139742479902942</v>
       </c>
       <c r="D224" t="n">
-        <v>0.3428123077177103</v>
+        <v>0.3343176610348074</v>
       </c>
       <c r="E224" t="n">
-        <v>0.3586979479235118</v>
+        <v>0.3673468836070121</v>
       </c>
       <c r="F224" t="n">
-        <v>0.05905328165515062</v>
+        <v>0.05907814824939604</v>
       </c>
       <c r="G224" t="n">
-        <v>0.03411131583533367</v>
+        <v>0.03540279935419741</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.03636275776116543</v>
+        <v>0.0355210323897282</v>
       </c>
       <c r="B225" t="n">
-        <v>0.02869665041770038</v>
+        <v>0.02859217295114285</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1402662813928828</v>
+        <v>0.1397423050682769</v>
       </c>
       <c r="D225" t="n">
-        <v>0.342966918943447</v>
+        <v>0.3345568940394555</v>
       </c>
       <c r="E225" t="n">
-        <v>0.3585349451225735</v>
+        <v>0.3670941472318729</v>
       </c>
       <c r="F225" t="n">
-        <v>0.05905234740138277</v>
+        <v>0.05907789959136792</v>
       </c>
       <c r="G225" t="n">
-        <v>0.03412009896084787</v>
+        <v>0.03541554872815567</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0.03636207630614829</v>
+        <v>0.03552115579810081</v>
       </c>
       <c r="B226" t="n">
-        <v>0.02869936554668989</v>
+        <v>0.02859302101121657</v>
       </c>
       <c r="C226" t="n">
-        <v>0.1402652746911447</v>
+        <v>0.139743549180323</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3431028422054861</v>
+        <v>0.3347877003939146</v>
       </c>
       <c r="E226" t="n">
-        <v>0.358390389418304</v>
+        <v>0.3668489865094353</v>
       </c>
       <c r="F226" t="n">
-        <v>0.05905125957176646</v>
+        <v>0.05907758249367756</v>
       </c>
       <c r="G226" t="n">
-        <v>0.03412879226046042</v>
+        <v>0.03542800461333195</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0.03636139787420564</v>
+        <v>0.03552116427202641</v>
       </c>
       <c r="B227" t="n">
-        <v>0.02870198598398086</v>
+        <v>0.02859379271350333</v>
       </c>
       <c r="C227" t="n">
-        <v>0.1402650255544085</v>
+        <v>0.1397462917288351</v>
       </c>
       <c r="D227" t="n">
-        <v>0.3432214513730213</v>
+        <v>0.3350099239807284</v>
       </c>
       <c r="E227" t="n">
-        <v>0.358262710065875</v>
+        <v>0.3666114610720793</v>
       </c>
       <c r="F227" t="n">
-        <v>0.05904997947984979</v>
+        <v>0.05907715021405689</v>
       </c>
       <c r="G227" t="n">
-        <v>0.03413744966865925</v>
+        <v>0.03544021601877082</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.03636074292477135</v>
+        <v>0.0355210827840311</v>
       </c>
       <c r="B228" t="n">
-        <v>0.02870449281047997</v>
+        <v>0.02859448181786321</v>
       </c>
       <c r="C228" t="n">
-        <v>0.1402656842984048</v>
+        <v>0.1397505645942331</v>
       </c>
       <c r="D228" t="n">
-        <v>0.3433239871920151</v>
+        <v>0.3352232933369602</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3581504957006416</v>
+        <v>0.3663817883341759</v>
       </c>
       <c r="F228" t="n">
-        <v>0.05904847103288537</v>
+        <v>0.05907655374612307</v>
       </c>
       <c r="G228" t="n">
-        <v>0.03414612604080211</v>
+        <v>0.03545223538661363</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>0.03636013230013735</v>
+        <v>0.035520936754968</v>
       </c>
       <c r="B229" t="n">
-        <v>0.02870686920698502</v>
+        <v>0.02859508564664621</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1402673672403325</v>
+        <v>0.1397563543002741</v>
       </c>
       <c r="D229" t="n">
-        <v>0.3434115378286272</v>
+        <v>0.3354274294881381</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3580525169770941</v>
+        <v>0.3661603338419341</v>
       </c>
       <c r="F229" t="n">
-        <v>0.05904670142176265</v>
+        <v>0.05907574355855531</v>
       </c>
       <c r="G229" t="n">
-        <v>0.03415487502506099</v>
+        <v>0.03546411640948428</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0.03635958698968018</v>
+        <v>0.03552075181333367</v>
       </c>
       <c r="B230" t="n">
-        <v>0.02870910105113531</v>
+        <v>0.02859560516678594</v>
       </c>
       <c r="C230" t="n">
-        <v>0.1402701558009888</v>
+        <v>0.1397636059040282</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3434850286128588</v>
+        <v>0.3356218595344997</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3579677388048482</v>
+        <v>0.3659475943601136</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0590446417608415</v>
+        <v>0.05907467144224813</v>
       </c>
       <c r="G230" t="n">
-        <v>0.03416374697964732</v>
+        <v>0.0354759117789905</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0.0363591278927488</v>
+        <v>0.03552055355384038</v>
       </c>
       <c r="B231" t="n">
-        <v>0.02871117737641508</v>
+        <v>0.02859604490439869</v>
       </c>
       <c r="C231" t="n">
-        <v>0.1402740968492981</v>
+        <v>0.1397722280931193</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3435452209905681</v>
+        <v>0.3358060353019189</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3578953221791509</v>
+        <v>0.3657441747961332</v>
       </c>
       <c r="F231" t="n">
-        <v>0.05904226766608803</v>
+        <v>0.059073292370112</v>
       </c>
       <c r="G231" t="n">
-        <v>0.03417278704573121</v>
+        <v>0.03548767098047759</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>0.03635877558273648</v>
+        <v>0.03552036729757364</v>
       </c>
       <c r="B232" t="n">
-        <v>0.02871309066957674</v>
+        <v>0.02859641269565505</v>
       </c>
       <c r="C232" t="n">
-        <v>0.1402792041250056</v>
+        <v>0.1397820989963965</v>
       </c>
       <c r="D232" t="n">
-        <v>0.343592720345855</v>
+        <v>0.3359793563033412</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3578346160426648</v>
+        <v>0.3655507601828168</v>
       </c>
       <c r="F232" t="n">
-        <v>0.05903955976046869</v>
+        <v>0.05907156627843137</v>
       </c>
       <c r="G232" t="n">
-        <v>0.0341820334736927</v>
+        <v>0.03549943824578508</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0.03635855007649767</v>
+        <v>0.03552021785631987</v>
       </c>
       <c r="B233" t="n">
-        <v>0.02871483699451488</v>
+        <v>0.02859671928555981</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1402854605054365</v>
+        <v>0.1397930722087578</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3436279920172099</v>
+        <v>0.3361411961686645</v>
       </c>
       <c r="E233" t="n">
-        <v>0.3577851400226048</v>
+        <v>0.3653680840263758</v>
       </c>
       <c r="F233" t="n">
-        <v>0.05903650409894434</v>
+        <v>0.05906945968792263</v>
       </c>
       <c r="G233" t="n">
-        <v>0.03419151628479164</v>
+        <v>0.03551125076639973</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0.03635847061235525</v>
+        <v>0.03552012930400768</v>
       </c>
       <c r="B234" t="n">
-        <v>0.02871641594105802</v>
+        <v>0.02859697779358275</v>
       </c>
       <c r="C234" t="n">
-        <v>0.1402928208483406</v>
+        <v>0.1398049825839583</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3436513844505193</v>
+        <v>0.336290931586722</v>
       </c>
       <c r="E234" t="n">
-        <v>0.3577465593130508</v>
+        <v>0.3651968943802134</v>
       </c>
       <c r="F234" t="n">
-        <v>0.05903309250562266</v>
+        <v>0.0590669470964905</v>
       </c>
       <c r="G234" t="n">
-        <v>0.03420125632905369</v>
+        <v>0.03552313725502533</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0.036358555439269</v>
+        <v>0.03552012475816101</v>
       </c>
       <c r="B235" t="n">
-        <v>0.02871783040693344</v>
+        <v>0.02859720307192111</v>
       </c>
       <c r="C235" t="n">
-        <v>0.1403012151473682</v>
+        <v>0.139817651447874</v>
       </c>
       <c r="D235" t="n">
-        <v>0.34366315807736</v>
+        <v>0.3364279726777696</v>
       </c>
       <c r="E235" t="n">
-        <v>0.3577186533329466</v>
+        <v>0.3650379190275172</v>
       </c>
       <c r="F235" t="n">
-        <v>0.05902932281908367</v>
+        <v>0.05906401209150888</v>
       </c>
       <c r="G235" t="n">
-        <v>0.03421126477703886</v>
+        <v>0.03553511692524849</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0.03635882161925275</v>
+        <v>0.03552022617384865</v>
       </c>
       <c r="B236" t="n">
-        <v>0.02871908623140196</v>
+        <v>0.02859741098781533</v>
       </c>
       <c r="C236" t="n">
-        <v>0.1403105517371611</v>
+        <v>0.1398308910147624</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3436635182060102</v>
+        <v>0.3365517935970262</v>
       </c>
       <c r="E236" t="n">
-        <v>0.3577012801018438</v>
+        <v>0.3648918311433245</v>
       </c>
       <c r="F236" t="n">
-        <v>0.05902519904320411</v>
+        <v>0.05906064814572387</v>
       </c>
       <c r="G236" t="n">
-        <v>0.03422154306112597</v>
+        <v>0.03554719893749875</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>0.03635928484366361</v>
+        <v>0.0355204541519734</v>
       </c>
       <c r="B237" t="n">
-        <v>0.02872019170643884</v>
+        <v>0.02859761766595278</v>
       </c>
       <c r="C237" t="n">
-        <v>0.1403207203470106</v>
+        <v>0.1398445079322077</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3436526499910799</v>
+        <v>0.3366619620793862</v>
       </c>
       <c r="E237" t="n">
-        <v>0.357694338449951</v>
+        <v>0.3647592167571382</v>
       </c>
       <c r="F237" t="n">
-        <v>0.05902073140276728</v>
+        <v>0.05905685907679314</v>
       </c>
       <c r="G237" t="n">
-        <v>0.03423208325908841</v>
+        <v>0.03555938233654876</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0.03635995926298156</v>
+        <v>0.03552082776270395</v>
       </c>
       <c r="B238" t="n">
-        <v>0.02872115699645918</v>
+        <v>0.02859783872991402</v>
       </c>
       <c r="C238" t="n">
-        <v>0.1403315948806189</v>
+        <v>0.139858306016766</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3436307534470946</v>
+        <v>0.3367581666001252</v>
       </c>
       <c r="E238" t="n">
-        <v>0.3576977302178462</v>
+        <v>0.3646405452440561</v>
       </c>
       <c r="F238" t="n">
-        <v>0.05901593630303094</v>
+        <v>0.05905265916468918</v>
       </c>
       <c r="G238" t="n">
-        <v>0.03424286889196847</v>
+        <v>0.03557165648174558</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0.03636085732831613</v>
+        <v>0.03552136438361297</v>
       </c>
       <c r="B239" t="n">
-        <v>0.02872199350265261</v>
+        <v>0.02859808858211768</v>
       </c>
       <c r="C239" t="n">
-        <v>0.1403430358706556</v>
+        <v>0.1398720883550767</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3435980765002667</v>
+        <v>0.3368402398604288</v>
       </c>
       <c r="E239" t="n">
-        <v>0.3577113245157578</v>
+        <v>0.3645361439378031</v>
       </c>
       <c r="F239" t="n">
-        <v>0.05901083619196795</v>
+        <v>0.05904807293366093</v>
       </c>
       <c r="G239" t="n">
-        <v>0.03425387609038361</v>
+        <v>0.03558400194729977</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.03636198964269972</v>
+        <v>0.03552207955092132</v>
       </c>
       <c r="B240" t="n">
-        <v>0.02872271321105855</v>
+        <v>0.02859837975992957</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1403548926384224</v>
+        <v>0.1398856590237222</v>
       </c>
       <c r="D240" t="n">
-        <v>0.343554944240441</v>
+        <v>0.3369081774213872</v>
       </c>
       <c r="E240" t="n">
-        <v>0.3577349258746351</v>
+        <v>0.3644461777806653</v>
       </c>
       <c r="F240" t="n">
-        <v>0.05900545932384939</v>
+        <v>0.05904313461645633</v>
       </c>
       <c r="G240" t="n">
-        <v>0.03426507506889395</v>
+        <v>0.03559639184691813</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0.03636336481837608</v>
+        <v>0.03552298682155092</v>
       </c>
       <c r="B241" t="n">
-        <v>0.02872332806006359</v>
+        <v>0.02859872240094075</v>
       </c>
       <c r="C241" t="n">
-        <v>0.1403670052696936</v>
+        <v>0.1398988247156561</v>
       </c>
       <c r="D241" t="n">
-        <v>0.3435017828057361</v>
+        <v>0.3369621505064266</v>
       </c>
       <c r="E241" t="n">
-        <v>0.3577682477947129</v>
+        <v>0.3643706347115472</v>
       </c>
       <c r="F241" t="n">
-        <v>0.05899983941830434</v>
+        <v>0.05903788732806103</v>
       </c>
       <c r="G241" t="n">
-        <v>0.03427643183311369</v>
+        <v>0.03560879351581756</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.03636498933886863</v>
+        <v>0.03552409764316684</v>
       </c>
       <c r="B242" t="n">
-        <v>0.02872384936590204</v>
+        <v>0.02859912384331696</v>
       </c>
       <c r="C242" t="n">
-        <v>0.1403792065493603</v>
+        <v>0.1399113965514157</v>
       </c>
       <c r="D242" t="n">
-        <v>0.3434391366979036</v>
+        <v>0.3370025122615111</v>
       </c>
       <c r="E242" t="n">
-        <v>0.357810892794087</v>
+        <v>0.3643093172518374</v>
       </c>
       <c r="F242" t="n">
-        <v>0.05899401521539492</v>
+        <v>0.05903238198447195</v>
       </c>
       <c r="G242" t="n">
-        <v>0.03428791003848321</v>
+        <v>0.0356211704642803</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.03636686742049897</v>
+        <v>0.03552542122981501</v>
       </c>
       <c r="B243" t="n">
-        <v>0.02872428733141547</v>
+        <v>0.0285995883779319</v>
       </c>
       <c r="C243" t="n">
-        <v>0.140391324038051</v>
+        <v>0.139923192302685</v>
       </c>
       <c r="D243" t="n">
-        <v>0.3433676787599628</v>
+        <v>0.3370297970864447</v>
       </c>
       <c r="E243" t="n">
-        <v>0.3578623396255062</v>
+        <v>0.3642618404919092</v>
       </c>
       <c r="F243" t="n">
-        <v>0.05898802991730211</v>
+        <v>0.05902667600953632</v>
       </c>
       <c r="G243" t="n">
-        <v>0.0342994729072638</v>
+        <v>0.03563348450167768</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0.03636900087816771</v>
+        <v>0.03552696444176055</v>
       </c>
       <c r="B244" t="n">
-        <v>0.02872465066637876</v>
+        <v>0.02860011715871949</v>
       </c>
       <c r="C244" t="n">
-        <v>0.1404031824501367</v>
+        <v>0.1399340391716285</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3432882124808338</v>
+        <v>0.3370447130079967</v>
       </c>
       <c r="E244" t="n">
-        <v>0.3579219378816784</v>
+        <v>0.3642276364217473</v>
       </c>
       <c r="F244" t="n">
-        <v>0.05898193052699853</v>
+        <v>0.05902083187899059</v>
       </c>
       <c r="G244" t="n">
-        <v>0.03431108511580611</v>
+        <v>0.03564569791915674</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.03637138899243473</v>
+        <v>0.03552873166972939</v>
       </c>
       <c r="B245" t="n">
-        <v>0.02872494633038921</v>
+        <v>0.0286007082671898</v>
       </c>
       <c r="C245" t="n">
-        <v>0.1404146064667299</v>
+        <v>0.1399437771646815</v>
       </c>
       <c r="D245" t="n">
-        <v>0.3432016667255543</v>
+        <v>0.3370481274312337</v>
       </c>
       <c r="E245" t="n">
-        <v>0.3579889098480592</v>
+        <v>0.3642059642977382</v>
       </c>
       <c r="F245" t="n">
-        <v>0.05897576708118878</v>
+        <v>0.05901491555564523</v>
       </c>
       <c r="G245" t="n">
-        <v>0.0343227145556443</v>
+        <v>0.03565777561378198</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>0.03637402838453063</v>
+        <v>0.03553072472592778</v>
       </c>
       <c r="B246" t="n">
-        <v>0.02872517940648294</v>
+        <v>0.02860135691744801</v>
       </c>
       <c r="C246" t="n">
-        <v>0.1404254240392492</v>
+        <v>0.1399522629862279</v>
       </c>
       <c r="D246" t="n">
-        <v>0.3431090833870963</v>
+        <v>0.3370410469524917</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3580623591045814</v>
+        <v>0.364195926507191</v>
       </c>
       <c r="F246" t="n">
-        <v>0.05896959179461889</v>
+        <v>0.05900899487263896</v>
       </c>
       <c r="G246" t="n">
-        <v>0.03433433388344082</v>
+        <v>0.03566968703807456</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>0.03637691290574716</v>
+        <v>0.03553294274635271</v>
       </c>
       <c r="B247" t="n">
-        <v>0.02872535309978775</v>
+        <v>0.02860205578025724</v>
       </c>
       <c r="C247" t="n">
-        <v>0.1404354701900792</v>
+        <v>0.1399593742718497</v>
       </c>
       <c r="D247" t="n">
-        <v>0.3430115988067129</v>
+        <v>0.3370245922239455</v>
       </c>
       <c r="E247" t="n">
-        <v>0.3581412850848622</v>
+        <v>0.3641964891888758</v>
       </c>
       <c r="F247" t="n">
-        <v>0.05896345813303723</v>
+        <v>0.05900313792211916</v>
       </c>
       <c r="G247" t="n">
-        <v>0.03434592177977401</v>
+        <v>0.03568140786660039</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0.03638003354757213</v>
+        <v>0.03553538211108024</v>
       </c>
       <c r="B248" t="n">
-        <v>0.0287254688519637</v>
+        <v>0.02860279539935656</v>
       </c>
       <c r="C248" t="n">
-        <v>0.1404445911912413</v>
+        <v>0.1399650138934626</v>
       </c>
       <c r="D248" t="n">
-        <v>0.3429104200878306</v>
+        <v>0.3369999691056901</v>
       </c>
       <c r="E248" t="n">
-        <v>0.3582246026313308</v>
+        <v>0.3642065066994321</v>
       </c>
       <c r="F248" t="n">
-        <v>0.0589574198393337</v>
+        <v>0.05899741150484703</v>
       </c>
       <c r="G248" t="n">
-        <v>0.03435746385072784</v>
+        <v>0.03569292128613098</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.03638337838668599</v>
+        <v>0.0355380363906656</v>
       </c>
       <c r="B249" t="n">
-        <v>0.0287255265530766</v>
+        <v>0.02860356467049668</v>
       </c>
       <c r="C249" t="n">
-        <v>0.1404526489703183</v>
+        <v>0.1399691140133336</v>
       </c>
       <c r="D249" t="n">
-        <v>0.3428067976561875</v>
+        <v>0.3369684375094274</v>
       </c>
       <c r="E249" t="n">
-        <v>0.358311165360099</v>
+        <v>0.3642247488876185</v>
       </c>
       <c r="F249" t="n">
-        <v>0.05895152994779346</v>
+        <v>0.05899187969155054</v>
       </c>
       <c r="G249" t="n">
-        <v>0.03436895312583882</v>
+        <v>0.03570421883690759</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>0.03638693257420811</v>
+        <v>0.03554089632749576</v>
       </c>
       <c r="B250" t="n">
-        <v>0.02872552483049369</v>
+        <v>0.02860435135387676</v>
       </c>
       <c r="C250" t="n">
-        <v>0.140459525497451</v>
+        <v>0.13997163954335</v>
       </c>
       <c r="D250" t="n">
-        <v>0.3427019955727034</v>
+        <v>0.3369312794204982</v>
       </c>
       <c r="E250" t="n">
-        <v>0.3583997915811391</v>
+        <v>0.3642499300561388</v>
       </c>
       <c r="F250" t="n">
-        <v>0.05894583981954498</v>
+        <v>0.05898660253949638</v>
       </c>
       <c r="G250" t="n">
-        <v>0.03438039012446024</v>
+        <v>0.03571530075914396</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>0.03554394986063394</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.0286051425927811</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.1399725906861513</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.3368897675767938</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.3642807384560005</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.05898163499866011</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.03572617582897931</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>0.0355471822011082</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.02860592541533419</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.1399720042891301</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.3368451361861607</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.3643158651776859</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.05897702603084436</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.03573686069973647</v>
       </c>
     </row>
   </sheetData>
